--- a/season/2026/2026_season.xlsx
+++ b/season/2026/2026_season.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Games" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Stats" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Classification" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Games" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chapter Stats" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="By Classification" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Games'!$A$1:$L$801</definedName>
@@ -898,16 +898,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n"/>
+      <c r="A2" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B2" s="9">
         <f>IF(A2="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A2,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C2" s="4" t="n"/>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F2" s="11" t="n"/>
-      <c r="G2" s="4" t="n"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H2" s="11" t="n"/>
       <c r="I2" s="11" t="n"/>
       <c r="J2" s="9">
@@ -921,16 +935,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n"/>
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B3" s="9">
         <f>IF(A3="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A3,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F3" s="11" t="n"/>
-      <c r="G3" s="4" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H3" s="11" t="n"/>
       <c r="I3" s="11" t="n"/>
       <c r="J3" s="9">
@@ -944,16 +972,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n"/>
+      <c r="A4" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B4" s="9">
         <f>IF(A4="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A4,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F4" s="11" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H4" s="11" t="n"/>
       <c r="I4" s="11" t="n"/>
       <c r="J4" s="9">
@@ -967,16 +1009,30 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n"/>
+      <c r="A5" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B5" s="9">
         <f>IF(A5="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A5,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F5" s="11" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H5" s="11" t="n"/>
       <c r="I5" s="11" t="n"/>
       <c r="J5" s="9">
@@ -990,16 +1046,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n"/>
+      <c r="A6" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B6" s="9">
         <f>IF(A6="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A6,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C6" s="4" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Winner G17</t>
+        </is>
+      </c>
       <c r="F6" s="11" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Winner G18</t>
+        </is>
+      </c>
       <c r="H6" s="11" t="n"/>
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="9">
@@ -1013,16 +1083,30 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n"/>
+      <c r="A7" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B7" s="9">
         <f>IF(A7="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A7,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C7" s="4" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Winner G19</t>
+        </is>
+      </c>
       <c r="F7" s="11" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Winner G20</t>
+        </is>
+      </c>
       <c r="H7" s="11" t="n"/>
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="9">
@@ -1036,16 +1120,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
+      <c r="A8" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B8" s="9">
         <f>IF(A8="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A8,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C8" s="4" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F8" s="11" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H8" s="11" t="n"/>
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="9">
@@ -1059,16 +1157,30 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
+      <c r="A9" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B9" s="9">
         <f>IF(A9="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A9,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C9" s="4" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Winner G21</t>
+        </is>
+      </c>
       <c r="F9" s="11" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Winner G22</t>
+        </is>
+      </c>
       <c r="H9" s="11" t="n"/>
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="9">
@@ -1082,16 +1194,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
+      <c r="A10" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B10" s="9">
         <f>IF(A10="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A10,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C10" s="4" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Winner G23</t>
+        </is>
+      </c>
       <c r="F10" s="11" t="n"/>
-      <c r="G10" s="4" t="n"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Winner G24</t>
+        </is>
+      </c>
       <c r="H10" s="11" t="n"/>
       <c r="I10" s="11" t="n"/>
       <c r="J10" s="9">
@@ -1105,16 +1231,30 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
+      <c r="A11" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B11" s="9">
         <f>IF(A11="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A11,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C11" s="4" t="n"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Winner G25</t>
+        </is>
+      </c>
       <c r="F11" s="11" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Winner G26</t>
+        </is>
+      </c>
       <c r="H11" s="11" t="n"/>
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="9">
@@ -1128,16 +1268,30 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
+      <c r="A12" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B12" s="9">
         <f>IF(A12="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A12,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C12" s="4" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Winner G27</t>
+        </is>
+      </c>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Winner G28</t>
+        </is>
+      </c>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="9">
@@ -1151,16 +1305,30 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
+      <c r="A13" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B13" s="9">
         <f>IF(A13="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A13,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C13" s="4" t="n"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>1A D1</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F13" s="11" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H13" s="11" t="n"/>
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="9">
@@ -1174,16 +1342,30 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
+      <c r="A14" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B14" s="9">
         <f>IF(A14="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A14,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F14" s="11" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H14" s="11" t="n"/>
       <c r="I14" s="11" t="n"/>
       <c r="J14" s="9">
@@ -1197,16 +1379,30 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
+      <c r="A15" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B15" s="9">
         <f>IF(A15="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A15,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C15" s="4" t="n"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="9">
@@ -1220,16 +1416,30 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
+      <c r="A16" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B16" s="9">
         <f>IF(A16="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A16,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F16" s="11" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H16" s="11" t="n"/>
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="9">
@@ -1243,16 +1453,30 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
+      <c r="A17" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B17" s="9">
         <f>IF(A17="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A17,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F17" s="11" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H17" s="11" t="n"/>
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="9">
@@ -1266,16 +1490,30 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
+      <c r="A18" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B18" s="9">
         <f>IF(A18="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A18,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C18" s="4" t="n"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Winner G17</t>
+        </is>
+      </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="4" t="n"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Winner G18</t>
+        </is>
+      </c>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="9">
@@ -1289,16 +1527,30 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
+      <c r="A19" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B19" s="9">
         <f>IF(A19="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A19,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C19" s="4" t="n"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Winner G19</t>
+        </is>
+      </c>
       <c r="F19" s="11" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Winner G20</t>
+        </is>
+      </c>
       <c r="H19" s="11" t="n"/>
       <c r="I19" s="11" t="n"/>
       <c r="J19" s="9">
@@ -1312,16 +1564,30 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
+      <c r="A20" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B20" s="9">
         <f>IF(A20="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A20,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C20" s="4" t="n"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F20" s="11" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H20" s="11" t="n"/>
       <c r="I20" s="11" t="n"/>
       <c r="J20" s="9">
@@ -1335,16 +1601,30 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
+      <c r="A21" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B21" s="9">
         <f>IF(A21="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A21,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C21" s="4" t="n"/>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Winner G21</t>
+        </is>
+      </c>
       <c r="F21" s="11" t="n"/>
-      <c r="G21" s="4" t="n"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Winner G22</t>
+        </is>
+      </c>
       <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="9">
@@ -1358,16 +1638,30 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
+      <c r="A22" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B22" s="9">
         <f>IF(A22="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A22,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C22" s="4" t="n"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Winner G23</t>
+        </is>
+      </c>
       <c r="F22" s="11" t="n"/>
-      <c r="G22" s="4" t="n"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Winner G24</t>
+        </is>
+      </c>
       <c r="H22" s="11" t="n"/>
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="9">
@@ -1381,16 +1675,30 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
+      <c r="A23" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B23" s="9">
         <f>IF(A23="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A23,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C23" s="4" t="n"/>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Winner G25</t>
+        </is>
+      </c>
       <c r="F23" s="11" t="n"/>
-      <c r="G23" s="4" t="n"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Winner G26</t>
+        </is>
+      </c>
       <c r="H23" s="11" t="n"/>
       <c r="I23" s="11" t="n"/>
       <c r="J23" s="9">
@@ -1404,16 +1712,30 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
+      <c r="A24" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B24" s="9">
         <f>IF(A24="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A24,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C24" s="4" t="n"/>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Winner G27</t>
+        </is>
+      </c>
       <c r="F24" s="11" t="n"/>
-      <c r="G24" s="4" t="n"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Winner G28</t>
+        </is>
+      </c>
       <c r="H24" s="11" t="n"/>
       <c r="I24" s="11" t="n"/>
       <c r="J24" s="9">
@@ -1427,16 +1749,30 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
+      <c r="A25" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B25" s="9">
         <f>IF(A25="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A25,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C25" s="4" t="n"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>1A D2</t>
+        </is>
+      </c>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F25" s="11" t="n"/>
-      <c r="G25" s="4" t="n"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H25" s="11" t="n"/>
       <c r="I25" s="11" t="n"/>
       <c r="J25" s="9">
@@ -1450,16 +1786,30 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
+      <c r="A26" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B26" s="9">
         <f>IF(A26="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A26,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C26" s="4" t="n"/>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F26" s="11" t="n"/>
-      <c r="G26" s="4" t="n"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H26" s="11" t="n"/>
       <c r="I26" s="11" t="n"/>
       <c r="J26" s="9">
@@ -1473,16 +1823,30 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
+      <c r="A27" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B27" s="9">
         <f>IF(A27="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A27,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C27" s="4" t="n"/>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F27" s="11" t="n"/>
-      <c r="G27" s="4" t="n"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H27" s="11" t="n"/>
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="9">
@@ -1496,16 +1860,30 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
+      <c r="A28" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B28" s="9">
         <f>IF(A28="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A28,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C28" s="4" t="n"/>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F28" s="11" t="n"/>
-      <c r="G28" s="4" t="n"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H28" s="11" t="n"/>
       <c r="I28" s="11" t="n"/>
       <c r="J28" s="9">
@@ -1519,16 +1897,30 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
+      <c r="A29" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B29" s="9">
         <f>IF(A29="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A29,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C29" s="4" t="n"/>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F29" s="11" t="n"/>
-      <c r="G29" s="4" t="n"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H29" s="11" t="n"/>
       <c r="I29" s="11" t="n"/>
       <c r="J29" s="9">
@@ -1542,16 +1934,30 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
+      <c r="A30" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B30" s="9">
         <f>IF(A30="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A30,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C30" s="4" t="n"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F30" s="11" t="n"/>
-      <c r="G30" s="4" t="n"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H30" s="11" t="n"/>
       <c r="I30" s="11" t="n"/>
       <c r="J30" s="9">
@@ -1565,16 +1971,30 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
+      <c r="A31" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B31" s="9">
         <f>IF(A31="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A31,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C31" s="4" t="n"/>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F31" s="11" t="n"/>
-      <c r="G31" s="4" t="n"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H31" s="11" t="n"/>
       <c r="I31" s="11" t="n"/>
       <c r="J31" s="9">
@@ -1588,16 +2008,30 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
+      <c r="A32" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B32" s="9">
         <f>IF(A32="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A32,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C32" s="4" t="n"/>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F32" s="11" t="n"/>
-      <c r="G32" s="4" t="n"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H32" s="11" t="n"/>
       <c r="I32" s="11" t="n"/>
       <c r="J32" s="9">
@@ -1611,16 +2045,30 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
+      <c r="A33" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B33" s="9">
         <f>IF(A33="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A33,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C33" s="4" t="n"/>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F33" s="11" t="n"/>
-      <c r="G33" s="4" t="n"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H33" s="11" t="n"/>
       <c r="I33" s="11" t="n"/>
       <c r="J33" s="9">
@@ -1634,16 +2082,30 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
+      <c r="A34" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B34" s="9">
         <f>IF(A34="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A34,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C34" s="4" t="n"/>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F34" s="11" t="n"/>
-      <c r="G34" s="4" t="n"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H34" s="11" t="n"/>
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="9">
@@ -1657,16 +2119,30 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
+      <c r="A35" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B35" s="9">
         <f>IF(A35="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A35,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C35" s="4" t="n"/>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F35" s="11" t="n"/>
-      <c r="G35" s="4" t="n"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H35" s="11" t="n"/>
       <c r="I35" s="11" t="n"/>
       <c r="J35" s="9">
@@ -1680,16 +2156,30 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
+      <c r="A36" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B36" s="9">
         <f>IF(A36="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A36,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C36" s="4" t="n"/>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F36" s="11" t="n"/>
-      <c r="G36" s="4" t="n"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H36" s="11" t="n"/>
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="9">
@@ -1703,16 +2193,30 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
+      <c r="A37" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B37" s="9">
         <f>IF(A37="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A37,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C37" s="4" t="n"/>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F37" s="11" t="n"/>
-      <c r="G37" s="4" t="n"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H37" s="11" t="n"/>
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="9">
@@ -1726,16 +2230,30 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
+      <c r="A38" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B38" s="9">
         <f>IF(A38="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A38,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C38" s="4" t="n"/>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F38" s="11" t="n"/>
-      <c r="G38" s="4" t="n"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H38" s="11" t="n"/>
       <c r="I38" s="11" t="n"/>
       <c r="J38" s="9">
@@ -1749,16 +2267,30 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
+      <c r="A39" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B39" s="9">
         <f>IF(A39="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A39,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C39" s="4" t="n"/>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F39" s="11" t="n"/>
-      <c r="G39" s="4" t="n"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H39" s="11" t="n"/>
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="9">
@@ -1772,16 +2304,30 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
+      <c r="A40" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B40" s="9">
         <f>IF(A40="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A40,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C40" s="4" t="n"/>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F40" s="11" t="n"/>
-      <c r="G40" s="4" t="n"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H40" s="11" t="n"/>
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="9">
@@ -1795,16 +2341,30 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
+      <c r="A41" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B41" s="9">
         <f>IF(A41="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A41,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C41" s="4" t="n"/>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F41" s="11" t="n"/>
-      <c r="G41" s="4" t="n"/>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H41" s="11" t="n"/>
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="9">
@@ -1818,16 +2378,30 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n"/>
+      <c r="A42" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B42" s="9">
         <f>IF(A42="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A42,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C42" s="4" t="n"/>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F42" s="11" t="n"/>
-      <c r="G42" s="4" t="n"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H42" s="11" t="n"/>
       <c r="I42" s="11" t="n"/>
       <c r="J42" s="9">
@@ -1841,16 +2415,30 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n"/>
+      <c r="A43" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B43" s="9">
         <f>IF(A43="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A43,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C43" s="4" t="n"/>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F43" s="11" t="n"/>
-      <c r="G43" s="4" t="n"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H43" s="11" t="n"/>
       <c r="I43" s="11" t="n"/>
       <c r="J43" s="9">
@@ -1864,16 +2452,30 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="n"/>
+      <c r="A44" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B44" s="9">
         <f>IF(A44="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A44,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C44" s="4" t="n"/>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F44" s="11" t="n"/>
-      <c r="G44" s="4" t="n"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H44" s="11" t="n"/>
       <c r="I44" s="11" t="n"/>
       <c r="J44" s="9">
@@ -1887,16 +2489,30 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="n"/>
+      <c r="A45" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B45" s="9">
         <f>IF(A45="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A45,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C45" s="4" t="n"/>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F45" s="11" t="n"/>
-      <c r="G45" s="4" t="n"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H45" s="11" t="n"/>
       <c r="I45" s="11" t="n"/>
       <c r="J45" s="9">
@@ -1910,16 +2526,30 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="n"/>
+      <c r="A46" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="B46" s="9">
         <f>IF(A46="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A46,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C46" s="4" t="n"/>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>2A D1</t>
+        </is>
+      </c>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F46" s="11" t="n"/>
-      <c r="G46" s="4" t="n"/>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H46" s="11" t="n"/>
       <c r="I46" s="11" t="n"/>
       <c r="J46" s="9">
@@ -1933,16 +2563,30 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="n"/>
+      <c r="A47" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B47" s="9">
         <f>IF(A47="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A47,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C47" s="4" t="n"/>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F47" s="11" t="n"/>
-      <c r="G47" s="4" t="n"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H47" s="11" t="n"/>
       <c r="I47" s="11" t="n"/>
       <c r="J47" s="9">
@@ -1956,16 +2600,30 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="n"/>
+      <c r="A48" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B48" s="9">
         <f>IF(A48="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A48,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C48" s="4" t="n"/>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F48" s="11" t="n"/>
-      <c r="G48" s="4" t="n"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H48" s="11" t="n"/>
       <c r="I48" s="11" t="n"/>
       <c r="J48" s="9">
@@ -1979,16 +2637,30 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="n"/>
+      <c r="A49" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B49" s="9">
         <f>IF(A49="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A49,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C49" s="4" t="n"/>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F49" s="11" t="n"/>
-      <c r="G49" s="4" t="n"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H49" s="11" t="n"/>
       <c r="I49" s="11" t="n"/>
       <c r="J49" s="9">
@@ -2002,16 +2674,30 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="n"/>
+      <c r="A50" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B50" s="9">
         <f>IF(A50="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A50,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C50" s="4" t="n"/>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F50" s="11" t="n"/>
-      <c r="G50" s="4" t="n"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H50" s="11" t="n"/>
       <c r="I50" s="11" t="n"/>
       <c r="J50" s="9">
@@ -2025,16 +2711,30 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="n"/>
+      <c r="A51" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B51" s="9">
         <f>IF(A51="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A51,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C51" s="4" t="n"/>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F51" s="11" t="n"/>
-      <c r="G51" s="4" t="n"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H51" s="11" t="n"/>
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="9">
@@ -2048,16 +2748,30 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="n"/>
+      <c r="A52" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B52" s="9">
         <f>IF(A52="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A52,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C52" s="4" t="n"/>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F52" s="11" t="n"/>
-      <c r="G52" s="4" t="n"/>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H52" s="11" t="n"/>
       <c r="I52" s="11" t="n"/>
       <c r="J52" s="9">
@@ -2071,16 +2785,30 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="n"/>
+      <c r="A53" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B53" s="9">
         <f>IF(A53="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A53,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C53" s="4" t="n"/>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F53" s="11" t="n"/>
-      <c r="G53" s="4" t="n"/>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H53" s="11" t="n"/>
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="9">
@@ -2094,16 +2822,30 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="n"/>
+      <c r="A54" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B54" s="9">
         <f>IF(A54="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A54,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C54" s="4" t="n"/>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F54" s="11" t="n"/>
-      <c r="G54" s="4" t="n"/>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H54" s="11" t="n"/>
       <c r="I54" s="11" t="n"/>
       <c r="J54" s="9">
@@ -2117,16 +2859,30 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="n"/>
+      <c r="A55" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B55" s="9">
         <f>IF(A55="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A55,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C55" s="4" t="n"/>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F55" s="11" t="n"/>
-      <c r="G55" s="4" t="n"/>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H55" s="11" t="n"/>
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="9">
@@ -2140,16 +2896,30 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="n"/>
+      <c r="A56" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B56" s="9">
         <f>IF(A56="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A56,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C56" s="4" t="n"/>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F56" s="11" t="n"/>
-      <c r="G56" s="4" t="n"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H56" s="11" t="n"/>
       <c r="I56" s="11" t="n"/>
       <c r="J56" s="9">
@@ -2163,16 +2933,30 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="n"/>
+      <c r="A57" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B57" s="9">
         <f>IF(A57="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A57,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C57" s="4" t="n"/>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F57" s="11" t="n"/>
-      <c r="G57" s="4" t="n"/>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H57" s="11" t="n"/>
       <c r="I57" s="11" t="n"/>
       <c r="J57" s="9">
@@ -2186,16 +2970,30 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="n"/>
+      <c r="A58" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B58" s="9">
         <f>IF(A58="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A58,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C58" s="4" t="n"/>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F58" s="11" t="n"/>
-      <c r="G58" s="4" t="n"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H58" s="11" t="n"/>
       <c r="I58" s="11" t="n"/>
       <c r="J58" s="9">
@@ -2209,16 +3007,30 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="n"/>
+      <c r="A59" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B59" s="9">
         <f>IF(A59="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A59,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C59" s="4" t="n"/>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F59" s="11" t="n"/>
-      <c r="G59" s="4" t="n"/>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H59" s="11" t="n"/>
       <c r="I59" s="11" t="n"/>
       <c r="J59" s="9">
@@ -2232,16 +3044,30 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="n"/>
+      <c r="A60" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B60" s="9">
         <f>IF(A60="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A60,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C60" s="4" t="n"/>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F60" s="11" t="n"/>
-      <c r="G60" s="4" t="n"/>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H60" s="11" t="n"/>
       <c r="I60" s="11" t="n"/>
       <c r="J60" s="9">
@@ -2255,16 +3081,30 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="n"/>
+      <c r="A61" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B61" s="9">
         <f>IF(A61="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A61,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C61" s="4" t="n"/>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F61" s="11" t="n"/>
-      <c r="G61" s="4" t="n"/>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H61" s="11" t="n"/>
       <c r="I61" s="11" t="n"/>
       <c r="J61" s="9">
@@ -2278,16 +3118,30 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="n"/>
+      <c r="A62" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B62" s="9">
         <f>IF(A62="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A62,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C62" s="4" t="n"/>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F62" s="11" t="n"/>
-      <c r="G62" s="4" t="n"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H62" s="11" t="n"/>
       <c r="I62" s="11" t="n"/>
       <c r="J62" s="9">
@@ -2301,16 +3155,30 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="n"/>
+      <c r="A63" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B63" s="9">
         <f>IF(A63="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A63,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C63" s="4" t="n"/>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F63" s="11" t="n"/>
-      <c r="G63" s="4" t="n"/>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H63" s="11" t="n"/>
       <c r="I63" s="11" t="n"/>
       <c r="J63" s="9">
@@ -2324,16 +3192,30 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="n"/>
+      <c r="A64" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B64" s="9">
         <f>IF(A64="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A64,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C64" s="4" t="n"/>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F64" s="11" t="n"/>
-      <c r="G64" s="4" t="n"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H64" s="11" t="n"/>
       <c r="I64" s="11" t="n"/>
       <c r="J64" s="9">
@@ -2347,16 +3229,30 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="n"/>
+      <c r="A65" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B65" s="9">
         <f>IF(A65="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A65,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C65" s="4" t="n"/>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F65" s="11" t="n"/>
-      <c r="G65" s="4" t="n"/>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H65" s="11" t="n"/>
       <c r="I65" s="11" t="n"/>
       <c r="J65" s="9">
@@ -2370,16 +3266,30 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="n"/>
+      <c r="A66" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B66" s="9">
         <f>IF(A66="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A66,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C66" s="4" t="n"/>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F66" s="11" t="n"/>
-      <c r="G66" s="4" t="n"/>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H66" s="11" t="n"/>
       <c r="I66" s="11" t="n"/>
       <c r="J66" s="9">
@@ -2393,16 +3303,30 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="n"/>
+      <c r="A67" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B67" s="9">
         <f>IF(A67="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A67,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C67" s="4" t="n"/>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>2A D2</t>
+        </is>
+      </c>
       <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F67" s="11" t="n"/>
-      <c r="G67" s="4" t="n"/>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H67" s="11" t="n"/>
       <c r="I67" s="11" t="n"/>
       <c r="J67" s="9">
@@ -2416,16 +3340,30 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="n"/>
+      <c r="A68" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B68" s="9">
         <f>IF(A68="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A68,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C68" s="4" t="n"/>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F68" s="11" t="n"/>
-      <c r="G68" s="4" t="n"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H68" s="11" t="n"/>
       <c r="I68" s="11" t="n"/>
       <c r="J68" s="9">
@@ -2439,16 +3377,30 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="n"/>
+      <c r="A69" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B69" s="9">
         <f>IF(A69="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A69,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C69" s="4" t="n"/>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="n"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F69" s="11" t="n"/>
-      <c r="G69" s="4" t="n"/>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H69" s="11" t="n"/>
       <c r="I69" s="11" t="n"/>
       <c r="J69" s="9">
@@ -2462,16 +3414,30 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="n"/>
+      <c r="A70" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B70" s="9">
         <f>IF(A70="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A70,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C70" s="4" t="n"/>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F70" s="11" t="n"/>
-      <c r="G70" s="4" t="n"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H70" s="11" t="n"/>
       <c r="I70" s="11" t="n"/>
       <c r="J70" s="9">
@@ -2485,16 +3451,30 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="n"/>
+      <c r="A71" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B71" s="9">
         <f>IF(A71="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A71,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C71" s="4" t="n"/>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F71" s="11" t="n"/>
-      <c r="G71" s="4" t="n"/>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H71" s="11" t="n"/>
       <c r="I71" s="11" t="n"/>
       <c r="J71" s="9">
@@ -2508,16 +3488,30 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="n"/>
+      <c r="A72" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B72" s="9">
         <f>IF(A72="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A72,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C72" s="4" t="n"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F72" s="11" t="n"/>
-      <c r="G72" s="4" t="n"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H72" s="11" t="n"/>
       <c r="I72" s="11" t="n"/>
       <c r="J72" s="9">
@@ -2531,16 +3525,30 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="n"/>
+      <c r="A73" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B73" s="9">
         <f>IF(A73="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A73,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C73" s="4" t="n"/>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F73" s="11" t="n"/>
-      <c r="G73" s="4" t="n"/>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H73" s="11" t="n"/>
       <c r="I73" s="11" t="n"/>
       <c r="J73" s="9">
@@ -2554,16 +3562,30 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="11" t="n"/>
+      <c r="A74" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B74" s="9">
         <f>IF(A74="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A74,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C74" s="4" t="n"/>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F74" s="11" t="n"/>
-      <c r="G74" s="4" t="n"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H74" s="11" t="n"/>
       <c r="I74" s="11" t="n"/>
       <c r="J74" s="9">
@@ -2577,16 +3599,30 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="n"/>
+      <c r="A75" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B75" s="9">
         <f>IF(A75="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A75,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C75" s="4" t="n"/>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F75" s="11" t="n"/>
-      <c r="G75" s="4" t="n"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H75" s="11" t="n"/>
       <c r="I75" s="11" t="n"/>
       <c r="J75" s="9">
@@ -2600,16 +3636,30 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="n"/>
+      <c r="A76" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B76" s="9">
         <f>IF(A76="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A76,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C76" s="4" t="n"/>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="n"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F76" s="11" t="n"/>
-      <c r="G76" s="4" t="n"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H76" s="11" t="n"/>
       <c r="I76" s="11" t="n"/>
       <c r="J76" s="9">
@@ -2623,16 +3673,30 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="n"/>
+      <c r="A77" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B77" s="9">
         <f>IF(A77="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A77,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C77" s="4" t="n"/>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F77" s="11" t="n"/>
-      <c r="G77" s="4" t="n"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H77" s="11" t="n"/>
       <c r="I77" s="11" t="n"/>
       <c r="J77" s="9">
@@ -2646,16 +3710,30 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="n"/>
+      <c r="A78" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B78" s="9">
         <f>IF(A78="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A78,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C78" s="4" t="n"/>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="n"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F78" s="11" t="n"/>
-      <c r="G78" s="4" t="n"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H78" s="11" t="n"/>
       <c r="I78" s="11" t="n"/>
       <c r="J78" s="9">
@@ -2669,16 +3747,30 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="n"/>
+      <c r="A79" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B79" s="9">
         <f>IF(A79="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A79,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C79" s="4" t="n"/>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F79" s="11" t="n"/>
-      <c r="G79" s="4" t="n"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H79" s="11" t="n"/>
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="9">
@@ -2692,16 +3784,30 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="n"/>
+      <c r="A80" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B80" s="9">
         <f>IF(A80="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A80,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C80" s="4" t="n"/>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F80" s="11" t="n"/>
-      <c r="G80" s="4" t="n"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H80" s="11" t="n"/>
       <c r="I80" s="11" t="n"/>
       <c r="J80" s="9">
@@ -2715,16 +3821,30 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="n"/>
+      <c r="A81" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B81" s="9">
         <f>IF(A81="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A81,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C81" s="4" t="n"/>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F81" s="11" t="n"/>
-      <c r="G81" s="4" t="n"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H81" s="11" t="n"/>
       <c r="I81" s="11" t="n"/>
       <c r="J81" s="9">
@@ -2738,16 +3858,30 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="n"/>
+      <c r="A82" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B82" s="9">
         <f>IF(A82="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A82,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C82" s="4" t="n"/>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F82" s="11" t="n"/>
-      <c r="G82" s="4" t="n"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H82" s="11" t="n"/>
       <c r="I82" s="11" t="n"/>
       <c r="J82" s="9">
@@ -2761,16 +3895,30 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="11" t="n"/>
+      <c r="A83" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B83" s="9">
         <f>IF(A83="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A83,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C83" s="4" t="n"/>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="n"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F83" s="11" t="n"/>
-      <c r="G83" s="4" t="n"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H83" s="11" t="n"/>
       <c r="I83" s="11" t="n"/>
       <c r="J83" s="9">
@@ -2784,16 +3932,30 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="n"/>
+      <c r="A84" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B84" s="9">
         <f>IF(A84="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A84,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C84" s="4" t="n"/>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="n"/>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F84" s="11" t="n"/>
-      <c r="G84" s="4" t="n"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H84" s="11" t="n"/>
       <c r="I84" s="11" t="n"/>
       <c r="J84" s="9">
@@ -2807,16 +3969,30 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="n"/>
+      <c r="A85" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B85" s="9">
         <f>IF(A85="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A85,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C85" s="4" t="n"/>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D85" s="4" t="n"/>
-      <c r="E85" s="4" t="n"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F85" s="11" t="n"/>
-      <c r="G85" s="4" t="n"/>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H85" s="11" t="n"/>
       <c r="I85" s="11" t="n"/>
       <c r="J85" s="9">
@@ -2830,16 +4006,30 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="11" t="n"/>
+      <c r="A86" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B86" s="9">
         <f>IF(A86="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A86,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C86" s="4" t="n"/>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n"/>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F86" s="11" t="n"/>
-      <c r="G86" s="4" t="n"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H86" s="11" t="n"/>
       <c r="I86" s="11" t="n"/>
       <c r="J86" s="9">
@@ -2853,16 +4043,30 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="n"/>
+      <c r="A87" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B87" s="9">
         <f>IF(A87="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A87,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C87" s="4" t="n"/>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="n"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F87" s="11" t="n"/>
-      <c r="G87" s="4" t="n"/>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H87" s="11" t="n"/>
       <c r="I87" s="11" t="n"/>
       <c r="J87" s="9">
@@ -2876,16 +4080,30 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="n"/>
+      <c r="A88" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="B88" s="9">
         <f>IF(A88="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A88,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C88" s="4" t="n"/>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>3A D1</t>
+        </is>
+      </c>
       <c r="D88" s="4" t="n"/>
-      <c r="E88" s="4" t="n"/>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F88" s="11" t="n"/>
-      <c r="G88" s="4" t="n"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H88" s="11" t="n"/>
       <c r="I88" s="11" t="n"/>
       <c r="J88" s="9">
@@ -2899,16 +4117,30 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="n"/>
+      <c r="A89" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B89" s="9">
         <f>IF(A89="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A89,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C89" s="4" t="n"/>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F89" s="11" t="n"/>
-      <c r="G89" s="4" t="n"/>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H89" s="11" t="n"/>
       <c r="I89" s="11" t="n"/>
       <c r="J89" s="9">
@@ -2922,16 +4154,30 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="11" t="n"/>
+      <c r="A90" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B90" s="9">
         <f>IF(A90="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A90,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C90" s="4" t="n"/>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="n"/>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F90" s="11" t="n"/>
-      <c r="G90" s="4" t="n"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H90" s="11" t="n"/>
       <c r="I90" s="11" t="n"/>
       <c r="J90" s="9">
@@ -2945,16 +4191,30 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="11" t="n"/>
+      <c r="A91" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B91" s="9">
         <f>IF(A91="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A91,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C91" s="4" t="n"/>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F91" s="11" t="n"/>
-      <c r="G91" s="4" t="n"/>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H91" s="11" t="n"/>
       <c r="I91" s="11" t="n"/>
       <c r="J91" s="9">
@@ -2968,16 +4228,30 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="n"/>
+      <c r="A92" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B92" s="9">
         <f>IF(A92="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A92,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C92" s="4" t="n"/>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="n"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F92" s="11" t="n"/>
-      <c r="G92" s="4" t="n"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H92" s="11" t="n"/>
       <c r="I92" s="11" t="n"/>
       <c r="J92" s="9">
@@ -2991,16 +4265,30 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="n"/>
+      <c r="A93" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B93" s="9">
         <f>IF(A93="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A93,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C93" s="4" t="n"/>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="n"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F93" s="11" t="n"/>
-      <c r="G93" s="4" t="n"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H93" s="11" t="n"/>
       <c r="I93" s="11" t="n"/>
       <c r="J93" s="9">
@@ -3014,16 +4302,30 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="11" t="n"/>
+      <c r="A94" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B94" s="9">
         <f>IF(A94="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A94,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C94" s="4" t="n"/>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D94" s="4" t="n"/>
-      <c r="E94" s="4" t="n"/>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F94" s="11" t="n"/>
-      <c r="G94" s="4" t="n"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H94" s="11" t="n"/>
       <c r="I94" s="11" t="n"/>
       <c r="J94" s="9">
@@ -3037,16 +4339,30 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="n"/>
+      <c r="A95" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B95" s="9">
         <f>IF(A95="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A95,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C95" s="4" t="n"/>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="n"/>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F95" s="11" t="n"/>
-      <c r="G95" s="4" t="n"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H95" s="11" t="n"/>
       <c r="I95" s="11" t="n"/>
       <c r="J95" s="9">
@@ -3060,16 +4376,30 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="11" t="n"/>
+      <c r="A96" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B96" s="9">
         <f>IF(A96="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A96,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C96" s="4" t="n"/>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F96" s="11" t="n"/>
-      <c r="G96" s="4" t="n"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H96" s="11" t="n"/>
       <c r="I96" s="11" t="n"/>
       <c r="J96" s="9">
@@ -3083,16 +4413,30 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="11" t="n"/>
+      <c r="A97" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B97" s="9">
         <f>IF(A97="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A97,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C97" s="4" t="n"/>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="n"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F97" s="11" t="n"/>
-      <c r="G97" s="4" t="n"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H97" s="11" t="n"/>
       <c r="I97" s="11" t="n"/>
       <c r="J97" s="9">
@@ -3106,16 +4450,30 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="11" t="n"/>
+      <c r="A98" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B98" s="9">
         <f>IF(A98="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A98,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C98" s="4" t="n"/>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="n"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F98" s="11" t="n"/>
-      <c r="G98" s="4" t="n"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H98" s="11" t="n"/>
       <c r="I98" s="11" t="n"/>
       <c r="J98" s="9">
@@ -3129,16 +4487,30 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="n"/>
+      <c r="A99" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B99" s="9">
         <f>IF(A99="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A99,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C99" s="4" t="n"/>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D99" s="4" t="n"/>
-      <c r="E99" s="4" t="n"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F99" s="11" t="n"/>
-      <c r="G99" s="4" t="n"/>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H99" s="11" t="n"/>
       <c r="I99" s="11" t="n"/>
       <c r="J99" s="9">
@@ -3152,16 +4524,30 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="n"/>
+      <c r="A100" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B100" s="9">
         <f>IF(A100="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A100,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C100" s="4" t="n"/>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F100" s="11" t="n"/>
-      <c r="G100" s="4" t="n"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H100" s="11" t="n"/>
       <c r="I100" s="11" t="n"/>
       <c r="J100" s="9">
@@ -3175,16 +4561,30 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="n"/>
+      <c r="A101" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B101" s="9">
         <f>IF(A101="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A101,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C101" s="4" t="n"/>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="n"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F101" s="11" t="n"/>
-      <c r="G101" s="4" t="n"/>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H101" s="11" t="n"/>
       <c r="I101" s="11" t="n"/>
       <c r="J101" s="9">
@@ -3198,16 +4598,30 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="n"/>
+      <c r="A102" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B102" s="9">
         <f>IF(A102="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A102,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C102" s="4" t="n"/>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F102" s="11" t="n"/>
-      <c r="G102" s="4" t="n"/>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H102" s="11" t="n"/>
       <c r="I102" s="11" t="n"/>
       <c r="J102" s="9">
@@ -3221,16 +4635,30 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="n"/>
+      <c r="A103" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B103" s="9">
         <f>IF(A103="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A103,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C103" s="4" t="n"/>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D103" s="4" t="n"/>
-      <c r="E103" s="4" t="n"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F103" s="11" t="n"/>
-      <c r="G103" s="4" t="n"/>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H103" s="11" t="n"/>
       <c r="I103" s="11" t="n"/>
       <c r="J103" s="9">
@@ -3244,16 +4672,30 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="11" t="n"/>
+      <c r="A104" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B104" s="9">
         <f>IF(A104="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A104,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C104" s="4" t="n"/>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D104" s="4" t="n"/>
-      <c r="E104" s="4" t="n"/>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F104" s="11" t="n"/>
-      <c r="G104" s="4" t="n"/>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H104" s="11" t="n"/>
       <c r="I104" s="11" t="n"/>
       <c r="J104" s="9">
@@ -3267,16 +4709,30 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="n"/>
+      <c r="A105" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B105" s="9">
         <f>IF(A105="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A105,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C105" s="4" t="n"/>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D105" s="4" t="n"/>
-      <c r="E105" s="4" t="n"/>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F105" s="11" t="n"/>
-      <c r="G105" s="4" t="n"/>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H105" s="11" t="n"/>
       <c r="I105" s="11" t="n"/>
       <c r="J105" s="9">
@@ -3290,16 +4746,30 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="11" t="n"/>
+      <c r="A106" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B106" s="9">
         <f>IF(A106="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A106,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C106" s="4" t="n"/>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D106" s="4" t="n"/>
-      <c r="E106" s="4" t="n"/>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F106" s="11" t="n"/>
-      <c r="G106" s="4" t="n"/>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H106" s="11" t="n"/>
       <c r="I106" s="11" t="n"/>
       <c r="J106" s="9">
@@ -3313,16 +4783,30 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="n"/>
+      <c r="A107" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B107" s="9">
         <f>IF(A107="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A107,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C107" s="4" t="n"/>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D107" s="4" t="n"/>
-      <c r="E107" s="4" t="n"/>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F107" s="11" t="n"/>
-      <c r="G107" s="4" t="n"/>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H107" s="11" t="n"/>
       <c r="I107" s="11" t="n"/>
       <c r="J107" s="9">
@@ -3336,16 +4820,30 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="11" t="n"/>
+      <c r="A108" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B108" s="9">
         <f>IF(A108="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A108,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C108" s="4" t="n"/>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D108" s="4" t="n"/>
-      <c r="E108" s="4" t="n"/>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F108" s="11" t="n"/>
-      <c r="G108" s="4" t="n"/>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H108" s="11" t="n"/>
       <c r="I108" s="11" t="n"/>
       <c r="J108" s="9">
@@ -3359,16 +4857,30 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="n"/>
+      <c r="A109" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="B109" s="9">
         <f>IF(A109="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A109,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C109" s="4" t="n"/>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>3A D2</t>
+        </is>
+      </c>
       <c r="D109" s="4" t="n"/>
-      <c r="E109" s="4" t="n"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F109" s="11" t="n"/>
-      <c r="G109" s="4" t="n"/>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H109" s="11" t="n"/>
       <c r="I109" s="11" t="n"/>
       <c r="J109" s="9">
@@ -3382,16 +4894,30 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="11" t="n"/>
+      <c r="A110" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B110" s="9">
         <f>IF(A110="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A110,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C110" s="4" t="n"/>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D110" s="4" t="n"/>
-      <c r="E110" s="4" t="n"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F110" s="11" t="n"/>
-      <c r="G110" s="4" t="n"/>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H110" s="11" t="n"/>
       <c r="I110" s="11" t="n"/>
       <c r="J110" s="9">
@@ -3405,16 +4931,30 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="11" t="n"/>
+      <c r="A111" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B111" s="9">
         <f>IF(A111="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A111,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C111" s="4" t="n"/>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D111" s="4" t="n"/>
-      <c r="E111" s="4" t="n"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F111" s="11" t="n"/>
-      <c r="G111" s="4" t="n"/>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H111" s="11" t="n"/>
       <c r="I111" s="11" t="n"/>
       <c r="J111" s="9">
@@ -3428,16 +4968,30 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="11" t="n"/>
+      <c r="A112" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B112" s="9">
         <f>IF(A112="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A112,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C112" s="4" t="n"/>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D112" s="4" t="n"/>
-      <c r="E112" s="4" t="n"/>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F112" s="11" t="n"/>
-      <c r="G112" s="4" t="n"/>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H112" s="11" t="n"/>
       <c r="I112" s="11" t="n"/>
       <c r="J112" s="9">
@@ -3451,16 +5005,30 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="11" t="n"/>
+      <c r="A113" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B113" s="9">
         <f>IF(A113="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A113,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C113" s="4" t="n"/>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="n"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F113" s="11" t="n"/>
-      <c r="G113" s="4" t="n"/>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H113" s="11" t="n"/>
       <c r="I113" s="11" t="n"/>
       <c r="J113" s="9">
@@ -3474,16 +5042,30 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="11" t="n"/>
+      <c r="A114" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B114" s="9">
         <f>IF(A114="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A114,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C114" s="4" t="n"/>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D114" s="4" t="n"/>
-      <c r="E114" s="4" t="n"/>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F114" s="11" t="n"/>
-      <c r="G114" s="4" t="n"/>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H114" s="11" t="n"/>
       <c r="I114" s="11" t="n"/>
       <c r="J114" s="9">
@@ -3497,16 +5079,30 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="11" t="n"/>
+      <c r="A115" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B115" s="9">
         <f>IF(A115="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A115,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C115" s="4" t="n"/>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D115" s="4" t="n"/>
-      <c r="E115" s="4" t="n"/>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F115" s="11" t="n"/>
-      <c r="G115" s="4" t="n"/>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H115" s="11" t="n"/>
       <c r="I115" s="11" t="n"/>
       <c r="J115" s="9">
@@ -3520,16 +5116,30 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="11" t="n"/>
+      <c r="A116" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B116" s="9">
         <f>IF(A116="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A116,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C116" s="4" t="n"/>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D116" s="4" t="n"/>
-      <c r="E116" s="4" t="n"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F116" s="11" t="n"/>
-      <c r="G116" s="4" t="n"/>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H116" s="11" t="n"/>
       <c r="I116" s="11" t="n"/>
       <c r="J116" s="9">
@@ -3543,16 +5153,30 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="11" t="n"/>
+      <c r="A117" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B117" s="9">
         <f>IF(A117="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A117,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C117" s="4" t="n"/>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D117" s="4" t="n"/>
-      <c r="E117" s="4" t="n"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F117" s="11" t="n"/>
-      <c r="G117" s="4" t="n"/>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H117" s="11" t="n"/>
       <c r="I117" s="11" t="n"/>
       <c r="J117" s="9">
@@ -3566,16 +5190,30 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="11" t="n"/>
+      <c r="A118" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B118" s="9">
         <f>IF(A118="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A118,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C118" s="4" t="n"/>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D118" s="4" t="n"/>
-      <c r="E118" s="4" t="n"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F118" s="11" t="n"/>
-      <c r="G118" s="4" t="n"/>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H118" s="11" t="n"/>
       <c r="I118" s="11" t="n"/>
       <c r="J118" s="9">
@@ -3589,16 +5227,30 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="11" t="n"/>
+      <c r="A119" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B119" s="9">
         <f>IF(A119="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A119,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C119" s="4" t="n"/>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D119" s="4" t="n"/>
-      <c r="E119" s="4" t="n"/>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F119" s="11" t="n"/>
-      <c r="G119" s="4" t="n"/>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H119" s="11" t="n"/>
       <c r="I119" s="11" t="n"/>
       <c r="J119" s="9">
@@ -3612,16 +5264,30 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="11" t="n"/>
+      <c r="A120" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B120" s="9">
         <f>IF(A120="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A120,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C120" s="4" t="n"/>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D120" s="4" t="n"/>
-      <c r="E120" s="4" t="n"/>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F120" s="11" t="n"/>
-      <c r="G120" s="4" t="n"/>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H120" s="11" t="n"/>
       <c r="I120" s="11" t="n"/>
       <c r="J120" s="9">
@@ -3635,16 +5301,30 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="11" t="n"/>
+      <c r="A121" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B121" s="9">
         <f>IF(A121="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A121,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C121" s="4" t="n"/>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D121" s="4" t="n"/>
-      <c r="E121" s="4" t="n"/>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F121" s="11" t="n"/>
-      <c r="G121" s="4" t="n"/>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H121" s="11" t="n"/>
       <c r="I121" s="11" t="n"/>
       <c r="J121" s="9">
@@ -3658,16 +5338,30 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="11" t="n"/>
+      <c r="A122" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B122" s="9">
         <f>IF(A122="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A122,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C122" s="4" t="n"/>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D122" s="4" t="n"/>
-      <c r="E122" s="4" t="n"/>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F122" s="11" t="n"/>
-      <c r="G122" s="4" t="n"/>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H122" s="11" t="n"/>
       <c r="I122" s="11" t="n"/>
       <c r="J122" s="9">
@@ -3681,16 +5375,30 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="11" t="n"/>
+      <c r="A123" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B123" s="9">
         <f>IF(A123="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A123,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C123" s="4" t="n"/>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D123" s="4" t="n"/>
-      <c r="E123" s="4" t="n"/>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F123" s="11" t="n"/>
-      <c r="G123" s="4" t="n"/>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H123" s="11" t="n"/>
       <c r="I123" s="11" t="n"/>
       <c r="J123" s="9">
@@ -3704,16 +5412,30 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="11" t="n"/>
+      <c r="A124" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B124" s="9">
         <f>IF(A124="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A124,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C124" s="4" t="n"/>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D124" s="4" t="n"/>
-      <c r="E124" s="4" t="n"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F124" s="11" t="n"/>
-      <c r="G124" s="4" t="n"/>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H124" s="11" t="n"/>
       <c r="I124" s="11" t="n"/>
       <c r="J124" s="9">
@@ -3727,16 +5449,30 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="11" t="n"/>
+      <c r="A125" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B125" s="9">
         <f>IF(A125="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A125,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C125" s="4" t="n"/>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D125" s="4" t="n"/>
-      <c r="E125" s="4" t="n"/>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F125" s="11" t="n"/>
-      <c r="G125" s="4" t="n"/>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H125" s="11" t="n"/>
       <c r="I125" s="11" t="n"/>
       <c r="J125" s="9">
@@ -3750,16 +5486,30 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="11" t="n"/>
+      <c r="A126" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B126" s="9">
         <f>IF(A126="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A126,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C126" s="4" t="n"/>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D126" s="4" t="n"/>
-      <c r="E126" s="4" t="n"/>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F126" s="11" t="n"/>
-      <c r="G126" s="4" t="n"/>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H126" s="11" t="n"/>
       <c r="I126" s="11" t="n"/>
       <c r="J126" s="9">
@@ -3773,16 +5523,30 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="11" t="n"/>
+      <c r="A127" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B127" s="9">
         <f>IF(A127="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A127,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C127" s="4" t="n"/>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D127" s="4" t="n"/>
-      <c r="E127" s="4" t="n"/>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F127" s="11" t="n"/>
-      <c r="G127" s="4" t="n"/>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H127" s="11" t="n"/>
       <c r="I127" s="11" t="n"/>
       <c r="J127" s="9">
@@ -3796,16 +5560,30 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="11" t="n"/>
+      <c r="A128" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B128" s="9">
         <f>IF(A128="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A128,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C128" s="4" t="n"/>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D128" s="4" t="n"/>
-      <c r="E128" s="4" t="n"/>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F128" s="11" t="n"/>
-      <c r="G128" s="4" t="n"/>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H128" s="11" t="n"/>
       <c r="I128" s="11" t="n"/>
       <c r="J128" s="9">
@@ -3819,16 +5597,30 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="11" t="n"/>
+      <c r="A129" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B129" s="9">
         <f>IF(A129="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A129,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C129" s="4" t="n"/>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D129" s="4" t="n"/>
-      <c r="E129" s="4" t="n"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F129" s="11" t="n"/>
-      <c r="G129" s="4" t="n"/>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H129" s="11" t="n"/>
       <c r="I129" s="11" t="n"/>
       <c r="J129" s="9">
@@ -3842,16 +5634,30 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="11" t="n"/>
+      <c r="A130" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="B130" s="9">
         <f>IF(A130="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A130,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C130" s="4" t="n"/>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>4A D1</t>
+        </is>
+      </c>
       <c r="D130" s="4" t="n"/>
-      <c r="E130" s="4" t="n"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F130" s="11" t="n"/>
-      <c r="G130" s="4" t="n"/>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H130" s="11" t="n"/>
       <c r="I130" s="11" t="n"/>
       <c r="J130" s="9">
@@ -3865,16 +5671,30 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="11" t="n"/>
+      <c r="A131" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B131" s="9">
         <f>IF(A131="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A131,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C131" s="4" t="n"/>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D131" s="4" t="n"/>
-      <c r="E131" s="4" t="n"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F131" s="11" t="n"/>
-      <c r="G131" s="4" t="n"/>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H131" s="11" t="n"/>
       <c r="I131" s="11" t="n"/>
       <c r="J131" s="9">
@@ -3888,16 +5708,30 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="11" t="n"/>
+      <c r="A132" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B132" s="9">
         <f>IF(A132="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A132,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C132" s="4" t="n"/>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D132" s="4" t="n"/>
-      <c r="E132" s="4" t="n"/>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F132" s="11" t="n"/>
-      <c r="G132" s="4" t="n"/>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H132" s="11" t="n"/>
       <c r="I132" s="11" t="n"/>
       <c r="J132" s="9">
@@ -3911,16 +5745,30 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="n"/>
+      <c r="A133" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B133" s="9">
         <f>IF(A133="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A133,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C133" s="4" t="n"/>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D133" s="4" t="n"/>
-      <c r="E133" s="4" t="n"/>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F133" s="11" t="n"/>
-      <c r="G133" s="4" t="n"/>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H133" s="11" t="n"/>
       <c r="I133" s="11" t="n"/>
       <c r="J133" s="9">
@@ -3934,16 +5782,30 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="11" t="n"/>
+      <c r="A134" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B134" s="9">
         <f>IF(A134="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A134,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C134" s="4" t="n"/>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D134" s="4" t="n"/>
-      <c r="E134" s="4" t="n"/>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F134" s="11" t="n"/>
-      <c r="G134" s="4" t="n"/>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H134" s="11" t="n"/>
       <c r="I134" s="11" t="n"/>
       <c r="J134" s="9">
@@ -3957,16 +5819,30 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="11" t="n"/>
+      <c r="A135" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B135" s="9">
         <f>IF(A135="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A135,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C135" s="4" t="n"/>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D135" s="4" t="n"/>
-      <c r="E135" s="4" t="n"/>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F135" s="11" t="n"/>
-      <c r="G135" s="4" t="n"/>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H135" s="11" t="n"/>
       <c r="I135" s="11" t="n"/>
       <c r="J135" s="9">
@@ -3980,16 +5856,30 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="11" t="n"/>
+      <c r="A136" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B136" s="9">
         <f>IF(A136="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A136,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C136" s="4" t="n"/>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D136" s="4" t="n"/>
-      <c r="E136" s="4" t="n"/>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F136" s="11" t="n"/>
-      <c r="G136" s="4" t="n"/>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H136" s="11" t="n"/>
       <c r="I136" s="11" t="n"/>
       <c r="J136" s="9">
@@ -4003,16 +5893,30 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="11" t="n"/>
+      <c r="A137" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B137" s="9">
         <f>IF(A137="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A137,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C137" s="4" t="n"/>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n"/>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F137" s="11" t="n"/>
-      <c r="G137" s="4" t="n"/>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H137" s="11" t="n"/>
       <c r="I137" s="11" t="n"/>
       <c r="J137" s="9">
@@ -4026,16 +5930,30 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="11" t="n"/>
+      <c r="A138" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B138" s="9">
         <f>IF(A138="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A138,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C138" s="4" t="n"/>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D138" s="4" t="n"/>
-      <c r="E138" s="4" t="n"/>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F138" s="11" t="n"/>
-      <c r="G138" s="4" t="n"/>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H138" s="11" t="n"/>
       <c r="I138" s="11" t="n"/>
       <c r="J138" s="9">
@@ -4049,16 +5967,30 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="11" t="n"/>
+      <c r="A139" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B139" s="9">
         <f>IF(A139="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A139,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C139" s="4" t="n"/>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D139" s="4" t="n"/>
-      <c r="E139" s="4" t="n"/>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F139" s="11" t="n"/>
-      <c r="G139" s="4" t="n"/>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H139" s="11" t="n"/>
       <c r="I139" s="11" t="n"/>
       <c r="J139" s="9">
@@ -4072,16 +6004,30 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="11" t="n"/>
+      <c r="A140" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B140" s="9">
         <f>IF(A140="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A140,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C140" s="4" t="n"/>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D140" s="4" t="n"/>
-      <c r="E140" s="4" t="n"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F140" s="11" t="n"/>
-      <c r="G140" s="4" t="n"/>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H140" s="11" t="n"/>
       <c r="I140" s="11" t="n"/>
       <c r="J140" s="9">
@@ -4095,16 +6041,30 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="11" t="n"/>
+      <c r="A141" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B141" s="9">
         <f>IF(A141="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A141,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C141" s="4" t="n"/>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D141" s="4" t="n"/>
-      <c r="E141" s="4" t="n"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F141" s="11" t="n"/>
-      <c r="G141" s="4" t="n"/>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H141" s="11" t="n"/>
       <c r="I141" s="11" t="n"/>
       <c r="J141" s="9">
@@ -4118,16 +6078,30 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="11" t="n"/>
+      <c r="A142" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B142" s="9">
         <f>IF(A142="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A142,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C142" s="4" t="n"/>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D142" s="4" t="n"/>
-      <c r="E142" s="4" t="n"/>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F142" s="11" t="n"/>
-      <c r="G142" s="4" t="n"/>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H142" s="11" t="n"/>
       <c r="I142" s="11" t="n"/>
       <c r="J142" s="9">
@@ -4141,16 +6115,30 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="11" t="n"/>
+      <c r="A143" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B143" s="9">
         <f>IF(A143="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A143,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C143" s="4" t="n"/>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D143" s="4" t="n"/>
-      <c r="E143" s="4" t="n"/>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F143" s="11" t="n"/>
-      <c r="G143" s="4" t="n"/>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H143" s="11" t="n"/>
       <c r="I143" s="11" t="n"/>
       <c r="J143" s="9">
@@ -4164,16 +6152,30 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="11" t="n"/>
+      <c r="A144" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B144" s="9">
         <f>IF(A144="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A144,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C144" s="4" t="n"/>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D144" s="4" t="n"/>
-      <c r="E144" s="4" t="n"/>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F144" s="11" t="n"/>
-      <c r="G144" s="4" t="n"/>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H144" s="11" t="n"/>
       <c r="I144" s="11" t="n"/>
       <c r="J144" s="9">
@@ -4187,16 +6189,30 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="11" t="n"/>
+      <c r="A145" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B145" s="9">
         <f>IF(A145="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A145,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C145" s="4" t="n"/>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D145" s="4" t="n"/>
-      <c r="E145" s="4" t="n"/>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F145" s="11" t="n"/>
-      <c r="G145" s="4" t="n"/>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H145" s="11" t="n"/>
       <c r="I145" s="11" t="n"/>
       <c r="J145" s="9">
@@ -4210,16 +6226,30 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="11" t="n"/>
+      <c r="A146" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B146" s="9">
         <f>IF(A146="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A146,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C146" s="4" t="n"/>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D146" s="4" t="n"/>
-      <c r="E146" s="4" t="n"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F146" s="11" t="n"/>
-      <c r="G146" s="4" t="n"/>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H146" s="11" t="n"/>
       <c r="I146" s="11" t="n"/>
       <c r="J146" s="9">
@@ -4233,16 +6263,30 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="11" t="n"/>
+      <c r="A147" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B147" s="9">
         <f>IF(A147="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A147,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C147" s="4" t="n"/>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D147" s="4" t="n"/>
-      <c r="E147" s="4" t="n"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F147" s="11" t="n"/>
-      <c r="G147" s="4" t="n"/>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H147" s="11" t="n"/>
       <c r="I147" s="11" t="n"/>
       <c r="J147" s="9">
@@ -4256,16 +6300,30 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="11" t="n"/>
+      <c r="A148" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B148" s="9">
         <f>IF(A148="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A148,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C148" s="4" t="n"/>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D148" s="4" t="n"/>
-      <c r="E148" s="4" t="n"/>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F148" s="11" t="n"/>
-      <c r="G148" s="4" t="n"/>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H148" s="11" t="n"/>
       <c r="I148" s="11" t="n"/>
       <c r="J148" s="9">
@@ -4279,16 +6337,30 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="11" t="n"/>
+      <c r="A149" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B149" s="9">
         <f>IF(A149="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A149,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C149" s="4" t="n"/>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D149" s="4" t="n"/>
-      <c r="E149" s="4" t="n"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F149" s="11" t="n"/>
-      <c r="G149" s="4" t="n"/>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H149" s="11" t="n"/>
       <c r="I149" s="11" t="n"/>
       <c r="J149" s="9">
@@ -4302,16 +6374,30 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="11" t="n"/>
+      <c r="A150" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B150" s="9">
         <f>IF(A150="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A150,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C150" s="4" t="n"/>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D150" s="4" t="n"/>
-      <c r="E150" s="4" t="n"/>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F150" s="11" t="n"/>
-      <c r="G150" s="4" t="n"/>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H150" s="11" t="n"/>
       <c r="I150" s="11" t="n"/>
       <c r="J150" s="9">
@@ -4325,16 +6411,30 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="11" t="n"/>
+      <c r="A151" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="B151" s="9">
         <f>IF(A151="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A151,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C151" s="4" t="n"/>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>4A D2</t>
+        </is>
+      </c>
       <c r="D151" s="4" t="n"/>
-      <c r="E151" s="4" t="n"/>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F151" s="11" t="n"/>
-      <c r="G151" s="4" t="n"/>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H151" s="11" t="n"/>
       <c r="I151" s="11" t="n"/>
       <c r="J151" s="9">
@@ -4348,16 +6448,30 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="11" t="n"/>
+      <c r="A152" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B152" s="9">
         <f>IF(A152="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A152,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C152" s="4" t="n"/>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D152" s="4" t="n"/>
-      <c r="E152" s="4" t="n"/>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F152" s="11" t="n"/>
-      <c r="G152" s="4" t="n"/>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H152" s="11" t="n"/>
       <c r="I152" s="11" t="n"/>
       <c r="J152" s="9">
@@ -4371,16 +6485,30 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="11" t="n"/>
+      <c r="A153" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B153" s="9">
         <f>IF(A153="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A153,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C153" s="4" t="n"/>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D153" s="4" t="n"/>
-      <c r="E153" s="4" t="n"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F153" s="11" t="n"/>
-      <c r="G153" s="4" t="n"/>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H153" s="11" t="n"/>
       <c r="I153" s="11" t="n"/>
       <c r="J153" s="9">
@@ -4394,16 +6522,30 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="11" t="n"/>
+      <c r="A154" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B154" s="9">
         <f>IF(A154="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A154,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C154" s="4" t="n"/>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D154" s="4" t="n"/>
-      <c r="E154" s="4" t="n"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F154" s="11" t="n"/>
-      <c r="G154" s="4" t="n"/>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H154" s="11" t="n"/>
       <c r="I154" s="11" t="n"/>
       <c r="J154" s="9">
@@ -4417,16 +6559,30 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="11" t="n"/>
+      <c r="A155" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B155" s="9">
         <f>IF(A155="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A155,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C155" s="4" t="n"/>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D155" s="4" t="n"/>
-      <c r="E155" s="4" t="n"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F155" s="11" t="n"/>
-      <c r="G155" s="4" t="n"/>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H155" s="11" t="n"/>
       <c r="I155" s="11" t="n"/>
       <c r="J155" s="9">
@@ -4440,16 +6596,30 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="11" t="n"/>
+      <c r="A156" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B156" s="9">
         <f>IF(A156="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A156,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C156" s="4" t="n"/>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D156" s="4" t="n"/>
-      <c r="E156" s="4" t="n"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F156" s="11" t="n"/>
-      <c r="G156" s="4" t="n"/>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H156" s="11" t="n"/>
       <c r="I156" s="11" t="n"/>
       <c r="J156" s="9">
@@ -4463,16 +6633,30 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="11" t="n"/>
+      <c r="A157" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B157" s="9">
         <f>IF(A157="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A157,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C157" s="4" t="n"/>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D157" s="4" t="n"/>
-      <c r="E157" s="4" t="n"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F157" s="11" t="n"/>
-      <c r="G157" s="4" t="n"/>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H157" s="11" t="n"/>
       <c r="I157" s="11" t="n"/>
       <c r="J157" s="9">
@@ -4486,16 +6670,30 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="11" t="n"/>
+      <c r="A158" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B158" s="9">
         <f>IF(A158="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A158,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C158" s="4" t="n"/>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D158" s="4" t="n"/>
-      <c r="E158" s="4" t="n"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F158" s="11" t="n"/>
-      <c r="G158" s="4" t="n"/>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H158" s="11" t="n"/>
       <c r="I158" s="11" t="n"/>
       <c r="J158" s="9">
@@ -4509,16 +6707,30 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="11" t="n"/>
+      <c r="A159" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B159" s="9">
         <f>IF(A159="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A159,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C159" s="4" t="n"/>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D159" s="4" t="n"/>
-      <c r="E159" s="4" t="n"/>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F159" s="11" t="n"/>
-      <c r="G159" s="4" t="n"/>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H159" s="11" t="n"/>
       <c r="I159" s="11" t="n"/>
       <c r="J159" s="9">
@@ -4532,16 +6744,30 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="11" t="n"/>
+      <c r="A160" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B160" s="9">
         <f>IF(A160="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A160,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C160" s="4" t="n"/>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D160" s="4" t="n"/>
-      <c r="E160" s="4" t="n"/>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F160" s="11" t="n"/>
-      <c r="G160" s="4" t="n"/>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H160" s="11" t="n"/>
       <c r="I160" s="11" t="n"/>
       <c r="J160" s="9">
@@ -4555,16 +6781,30 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="11" t="n"/>
+      <c r="A161" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B161" s="9">
         <f>IF(A161="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A161,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C161" s="4" t="n"/>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D161" s="4" t="n"/>
-      <c r="E161" s="4" t="n"/>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F161" s="11" t="n"/>
-      <c r="G161" s="4" t="n"/>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H161" s="11" t="n"/>
       <c r="I161" s="11" t="n"/>
       <c r="J161" s="9">
@@ -4578,16 +6818,30 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="11" t="n"/>
+      <c r="A162" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B162" s="9">
         <f>IF(A162="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A162,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C162" s="4" t="n"/>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D162" s="4" t="n"/>
-      <c r="E162" s="4" t="n"/>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F162" s="11" t="n"/>
-      <c r="G162" s="4" t="n"/>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H162" s="11" t="n"/>
       <c r="I162" s="11" t="n"/>
       <c r="J162" s="9">
@@ -4601,16 +6855,30 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="11" t="n"/>
+      <c r="A163" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B163" s="9">
         <f>IF(A163="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A163,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C163" s="4" t="n"/>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D163" s="4" t="n"/>
-      <c r="E163" s="4" t="n"/>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F163" s="11" t="n"/>
-      <c r="G163" s="4" t="n"/>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H163" s="11" t="n"/>
       <c r="I163" s="11" t="n"/>
       <c r="J163" s="9">
@@ -4624,16 +6892,30 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="11" t="n"/>
+      <c r="A164" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B164" s="9">
         <f>IF(A164="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A164,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C164" s="4" t="n"/>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D164" s="4" t="n"/>
-      <c r="E164" s="4" t="n"/>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F164" s="11" t="n"/>
-      <c r="G164" s="4" t="n"/>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H164" s="11" t="n"/>
       <c r="I164" s="11" t="n"/>
       <c r="J164" s="9">
@@ -4647,16 +6929,30 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="11" t="n"/>
+      <c r="A165" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B165" s="9">
         <f>IF(A165="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A165,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C165" s="4" t="n"/>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D165" s="4" t="n"/>
-      <c r="E165" s="4" t="n"/>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F165" s="11" t="n"/>
-      <c r="G165" s="4" t="n"/>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H165" s="11" t="n"/>
       <c r="I165" s="11" t="n"/>
       <c r="J165" s="9">
@@ -4670,16 +6966,30 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="11" t="n"/>
+      <c r="A166" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B166" s="9">
         <f>IF(A166="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A166,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C166" s="4" t="n"/>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D166" s="4" t="n"/>
-      <c r="E166" s="4" t="n"/>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F166" s="11" t="n"/>
-      <c r="G166" s="4" t="n"/>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H166" s="11" t="n"/>
       <c r="I166" s="11" t="n"/>
       <c r="J166" s="9">
@@ -4693,16 +7003,30 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="11" t="n"/>
+      <c r="A167" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B167" s="9">
         <f>IF(A167="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A167,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C167" s="4" t="n"/>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D167" s="4" t="n"/>
-      <c r="E167" s="4" t="n"/>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F167" s="11" t="n"/>
-      <c r="G167" s="4" t="n"/>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H167" s="11" t="n"/>
       <c r="I167" s="11" t="n"/>
       <c r="J167" s="9">
@@ -4716,16 +7040,30 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="11" t="n"/>
+      <c r="A168" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B168" s="9">
         <f>IF(A168="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A168,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C168" s="4" t="n"/>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D168" s="4" t="n"/>
-      <c r="E168" s="4" t="n"/>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F168" s="11" t="n"/>
-      <c r="G168" s="4" t="n"/>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H168" s="11" t="n"/>
       <c r="I168" s="11" t="n"/>
       <c r="J168" s="9">
@@ -4739,16 +7077,30 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="11" t="n"/>
+      <c r="A169" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B169" s="9">
         <f>IF(A169="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A169,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C169" s="4" t="n"/>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D169" s="4" t="n"/>
-      <c r="E169" s="4" t="n"/>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F169" s="11" t="n"/>
-      <c r="G169" s="4" t="n"/>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H169" s="11" t="n"/>
       <c r="I169" s="11" t="n"/>
       <c r="J169" s="9">
@@ -4762,16 +7114,30 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="11" t="n"/>
+      <c r="A170" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B170" s="9">
         <f>IF(A170="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A170,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C170" s="4" t="n"/>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D170" s="4" t="n"/>
-      <c r="E170" s="4" t="n"/>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F170" s="11" t="n"/>
-      <c r="G170" s="4" t="n"/>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H170" s="11" t="n"/>
       <c r="I170" s="11" t="n"/>
       <c r="J170" s="9">
@@ -4785,16 +7151,30 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="11" t="n"/>
+      <c r="A171" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B171" s="9">
         <f>IF(A171="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A171,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C171" s="4" t="n"/>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D171" s="4" t="n"/>
-      <c r="E171" s="4" t="n"/>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F171" s="11" t="n"/>
-      <c r="G171" s="4" t="n"/>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H171" s="11" t="n"/>
       <c r="I171" s="11" t="n"/>
       <c r="J171" s="9">
@@ -4808,16 +7188,30 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="11" t="n"/>
+      <c r="A172" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="B172" s="9">
         <f>IF(A172="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A172,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C172" s="4" t="n"/>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>5A D1</t>
+        </is>
+      </c>
       <c r="D172" s="4" t="n"/>
-      <c r="E172" s="4" t="n"/>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F172" s="11" t="n"/>
-      <c r="G172" s="4" t="n"/>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H172" s="11" t="n"/>
       <c r="I172" s="11" t="n"/>
       <c r="J172" s="9">
@@ -4831,16 +7225,30 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="11" t="n"/>
+      <c r="A173" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B173" s="9">
         <f>IF(A173="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A173,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C173" s="4" t="n"/>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D173" s="4" t="n"/>
-      <c r="E173" s="4" t="n"/>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F173" s="11" t="n"/>
-      <c r="G173" s="4" t="n"/>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H173" s="11" t="n"/>
       <c r="I173" s="11" t="n"/>
       <c r="J173" s="9">
@@ -4854,16 +7262,30 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="11" t="n"/>
+      <c r="A174" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B174" s="9">
         <f>IF(A174="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A174,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C174" s="4" t="n"/>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D174" s="4" t="n"/>
-      <c r="E174" s="4" t="n"/>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F174" s="11" t="n"/>
-      <c r="G174" s="4" t="n"/>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H174" s="11" t="n"/>
       <c r="I174" s="11" t="n"/>
       <c r="J174" s="9">
@@ -4877,16 +7299,30 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="11" t="n"/>
+      <c r="A175" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B175" s="9">
         <f>IF(A175="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A175,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C175" s="4" t="n"/>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D175" s="4" t="n"/>
-      <c r="E175" s="4" t="n"/>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F175" s="11" t="n"/>
-      <c r="G175" s="4" t="n"/>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H175" s="11" t="n"/>
       <c r="I175" s="11" t="n"/>
       <c r="J175" s="9">
@@ -4900,16 +7336,30 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="11" t="n"/>
+      <c r="A176" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B176" s="9">
         <f>IF(A176="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A176,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C176" s="4" t="n"/>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D176" s="4" t="n"/>
-      <c r="E176" s="4" t="n"/>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F176" s="11" t="n"/>
-      <c r="G176" s="4" t="n"/>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H176" s="11" t="n"/>
       <c r="I176" s="11" t="n"/>
       <c r="J176" s="9">
@@ -4923,16 +7373,30 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="11" t="n"/>
+      <c r="A177" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B177" s="9">
         <f>IF(A177="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A177,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C177" s="4" t="n"/>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D177" s="4" t="n"/>
-      <c r="E177" s="4" t="n"/>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F177" s="11" t="n"/>
-      <c r="G177" s="4" t="n"/>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H177" s="11" t="n"/>
       <c r="I177" s="11" t="n"/>
       <c r="J177" s="9">
@@ -4946,16 +7410,30 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="11" t="n"/>
+      <c r="A178" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B178" s="9">
         <f>IF(A178="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A178,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C178" s="4" t="n"/>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D178" s="4" t="n"/>
-      <c r="E178" s="4" t="n"/>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F178" s="11" t="n"/>
-      <c r="G178" s="4" t="n"/>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H178" s="11" t="n"/>
       <c r="I178" s="11" t="n"/>
       <c r="J178" s="9">
@@ -4969,16 +7447,30 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="11" t="n"/>
+      <c r="A179" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B179" s="9">
         <f>IF(A179="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A179,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C179" s="4" t="n"/>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D179" s="4" t="n"/>
-      <c r="E179" s="4" t="n"/>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F179" s="11" t="n"/>
-      <c r="G179" s="4" t="n"/>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H179" s="11" t="n"/>
       <c r="I179" s="11" t="n"/>
       <c r="J179" s="9">
@@ -4992,16 +7484,30 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="11" t="n"/>
+      <c r="A180" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B180" s="9">
         <f>IF(A180="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A180,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C180" s="4" t="n"/>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D180" s="4" t="n"/>
-      <c r="E180" s="4" t="n"/>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F180" s="11" t="n"/>
-      <c r="G180" s="4" t="n"/>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H180" s="11" t="n"/>
       <c r="I180" s="11" t="n"/>
       <c r="J180" s="9">
@@ -5015,16 +7521,30 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="11" t="n"/>
+      <c r="A181" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B181" s="9">
         <f>IF(A181="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A181,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C181" s="4" t="n"/>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D181" s="4" t="n"/>
-      <c r="E181" s="4" t="n"/>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F181" s="11" t="n"/>
-      <c r="G181" s="4" t="n"/>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H181" s="11" t="n"/>
       <c r="I181" s="11" t="n"/>
       <c r="J181" s="9">
@@ -5038,16 +7558,30 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="11" t="n"/>
+      <c r="A182" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B182" s="9">
         <f>IF(A182="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A182,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C182" s="4" t="n"/>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D182" s="4" t="n"/>
-      <c r="E182" s="4" t="n"/>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F182" s="11" t="n"/>
-      <c r="G182" s="4" t="n"/>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H182" s="11" t="n"/>
       <c r="I182" s="11" t="n"/>
       <c r="J182" s="9">
@@ -5061,16 +7595,30 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="11" t="n"/>
+      <c r="A183" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B183" s="9">
         <f>IF(A183="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A183,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C183" s="4" t="n"/>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D183" s="4" t="n"/>
-      <c r="E183" s="4" t="n"/>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F183" s="11" t="n"/>
-      <c r="G183" s="4" t="n"/>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H183" s="11" t="n"/>
       <c r="I183" s="11" t="n"/>
       <c r="J183" s="9">
@@ -5084,16 +7632,30 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="11" t="n"/>
+      <c r="A184" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B184" s="9">
         <f>IF(A184="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A184,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C184" s="4" t="n"/>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D184" s="4" t="n"/>
-      <c r="E184" s="4" t="n"/>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F184" s="11" t="n"/>
-      <c r="G184" s="4" t="n"/>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H184" s="11" t="n"/>
       <c r="I184" s="11" t="n"/>
       <c r="J184" s="9">
@@ -5107,16 +7669,30 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="11" t="n"/>
+      <c r="A185" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B185" s="9">
         <f>IF(A185="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A185,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C185" s="4" t="n"/>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D185" s="4" t="n"/>
-      <c r="E185" s="4" t="n"/>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F185" s="11" t="n"/>
-      <c r="G185" s="4" t="n"/>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H185" s="11" t="n"/>
       <c r="I185" s="11" t="n"/>
       <c r="J185" s="9">
@@ -5130,16 +7706,30 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="11" t="n"/>
+      <c r="A186" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B186" s="9">
         <f>IF(A186="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A186,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C186" s="4" t="n"/>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D186" s="4" t="n"/>
-      <c r="E186" s="4" t="n"/>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F186" s="11" t="n"/>
-      <c r="G186" s="4" t="n"/>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H186" s="11" t="n"/>
       <c r="I186" s="11" t="n"/>
       <c r="J186" s="9">
@@ -5153,16 +7743,30 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="11" t="n"/>
+      <c r="A187" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B187" s="9">
         <f>IF(A187="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A187,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C187" s="4" t="n"/>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D187" s="4" t="n"/>
-      <c r="E187" s="4" t="n"/>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F187" s="11" t="n"/>
-      <c r="G187" s="4" t="n"/>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H187" s="11" t="n"/>
       <c r="I187" s="11" t="n"/>
       <c r="J187" s="9">
@@ -5176,16 +7780,30 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="11" t="n"/>
+      <c r="A188" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B188" s="9">
         <f>IF(A188="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A188,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C188" s="4" t="n"/>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D188" s="4" t="n"/>
-      <c r="E188" s="4" t="n"/>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F188" s="11" t="n"/>
-      <c r="G188" s="4" t="n"/>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H188" s="11" t="n"/>
       <c r="I188" s="11" t="n"/>
       <c r="J188" s="9">
@@ -5199,16 +7817,30 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="11" t="n"/>
+      <c r="A189" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B189" s="9">
         <f>IF(A189="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A189,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C189" s="4" t="n"/>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D189" s="4" t="n"/>
-      <c r="E189" s="4" t="n"/>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F189" s="11" t="n"/>
-      <c r="G189" s="4" t="n"/>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H189" s="11" t="n"/>
       <c r="I189" s="11" t="n"/>
       <c r="J189" s="9">
@@ -5222,16 +7854,30 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="11" t="n"/>
+      <c r="A190" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B190" s="9">
         <f>IF(A190="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A190,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C190" s="4" t="n"/>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D190" s="4" t="n"/>
-      <c r="E190" s="4" t="n"/>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F190" s="11" t="n"/>
-      <c r="G190" s="4" t="n"/>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H190" s="11" t="n"/>
       <c r="I190" s="11" t="n"/>
       <c r="J190" s="9">
@@ -5245,16 +7891,30 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="11" t="n"/>
+      <c r="A191" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B191" s="9">
         <f>IF(A191="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A191,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C191" s="4" t="n"/>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D191" s="4" t="n"/>
-      <c r="E191" s="4" t="n"/>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F191" s="11" t="n"/>
-      <c r="G191" s="4" t="n"/>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H191" s="11" t="n"/>
       <c r="I191" s="11" t="n"/>
       <c r="J191" s="9">
@@ -5268,16 +7928,30 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="11" t="n"/>
+      <c r="A192" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B192" s="9">
         <f>IF(A192="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A192,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C192" s="4" t="n"/>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D192" s="4" t="n"/>
-      <c r="E192" s="4" t="n"/>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F192" s="11" t="n"/>
-      <c r="G192" s="4" t="n"/>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H192" s="11" t="n"/>
       <c r="I192" s="11" t="n"/>
       <c r="J192" s="9">
@@ -5291,16 +7965,30 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="11" t="n"/>
+      <c r="A193" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="B193" s="9">
         <f>IF(A193="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A193,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C193" s="4" t="n"/>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>5A D2</t>
+        </is>
+      </c>
       <c r="D193" s="4" t="n"/>
-      <c r="E193" s="4" t="n"/>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F193" s="11" t="n"/>
-      <c r="G193" s="4" t="n"/>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H193" s="11" t="n"/>
       <c r="I193" s="11" t="n"/>
       <c r="J193" s="9">
@@ -5314,16 +8002,30 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="11" t="n"/>
+      <c r="A194" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B194" s="9">
         <f>IF(A194="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A194,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C194" s="4" t="n"/>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D194" s="4" t="n"/>
-      <c r="E194" s="4" t="n"/>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F194" s="11" t="n"/>
-      <c r="G194" s="4" t="n"/>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H194" s="11" t="n"/>
       <c r="I194" s="11" t="n"/>
       <c r="J194" s="9">
@@ -5337,16 +8039,30 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="11" t="n"/>
+      <c r="A195" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B195" s="9">
         <f>IF(A195="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A195,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C195" s="4" t="n"/>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D195" s="4" t="n"/>
-      <c r="E195" s="4" t="n"/>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F195" s="11" t="n"/>
-      <c r="G195" s="4" t="n"/>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H195" s="11" t="n"/>
       <c r="I195" s="11" t="n"/>
       <c r="J195" s="9">
@@ -5360,16 +8076,30 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="11" t="n"/>
+      <c r="A196" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B196" s="9">
         <f>IF(A196="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A196,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C196" s="4" t="n"/>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D196" s="4" t="n"/>
-      <c r="E196" s="4" t="n"/>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F196" s="11" t="n"/>
-      <c r="G196" s="4" t="n"/>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H196" s="11" t="n"/>
       <c r="I196" s="11" t="n"/>
       <c r="J196" s="9">
@@ -5383,16 +8113,30 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="11" t="n"/>
+      <c r="A197" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B197" s="9">
         <f>IF(A197="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A197,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C197" s="4" t="n"/>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D197" s="4" t="n"/>
-      <c r="E197" s="4" t="n"/>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F197" s="11" t="n"/>
-      <c r="G197" s="4" t="n"/>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H197" s="11" t="n"/>
       <c r="I197" s="11" t="n"/>
       <c r="J197" s="9">
@@ -5406,16 +8150,30 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="11" t="n"/>
+      <c r="A198" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B198" s="9">
         <f>IF(A198="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A198,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C198" s="4" t="n"/>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D198" s="4" t="n"/>
-      <c r="E198" s="4" t="n"/>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F198" s="11" t="n"/>
-      <c r="G198" s="4" t="n"/>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H198" s="11" t="n"/>
       <c r="I198" s="11" t="n"/>
       <c r="J198" s="9">
@@ -5429,16 +8187,30 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="11" t="n"/>
+      <c r="A199" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B199" s="9">
         <f>IF(A199="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A199,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C199" s="4" t="n"/>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D199" s="4" t="n"/>
-      <c r="E199" s="4" t="n"/>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F199" s="11" t="n"/>
-      <c r="G199" s="4" t="n"/>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H199" s="11" t="n"/>
       <c r="I199" s="11" t="n"/>
       <c r="J199" s="9">
@@ -5452,16 +8224,30 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="11" t="n"/>
+      <c r="A200" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B200" s="9">
         <f>IF(A200="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A200,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C200" s="4" t="n"/>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D200" s="4" t="n"/>
-      <c r="E200" s="4" t="n"/>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F200" s="11" t="n"/>
-      <c r="G200" s="4" t="n"/>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H200" s="11" t="n"/>
       <c r="I200" s="11" t="n"/>
       <c r="J200" s="9">
@@ -5475,16 +8261,30 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="11" t="n"/>
+      <c r="A201" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B201" s="9">
         <f>IF(A201="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A201,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C201" s="4" t="n"/>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D201" s="4" t="n"/>
-      <c r="E201" s="4" t="n"/>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F201" s="11" t="n"/>
-      <c r="G201" s="4" t="n"/>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H201" s="11" t="n"/>
       <c r="I201" s="11" t="n"/>
       <c r="J201" s="9">
@@ -5498,16 +8298,30 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="11" t="n"/>
+      <c r="A202" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B202" s="9">
         <f>IF(A202="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A202,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C202" s="4" t="n"/>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D202" s="4" t="n"/>
-      <c r="E202" s="4" t="n"/>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F202" s="11" t="n"/>
-      <c r="G202" s="4" t="n"/>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H202" s="11" t="n"/>
       <c r="I202" s="11" t="n"/>
       <c r="J202" s="9">
@@ -5521,16 +8335,30 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="11" t="n"/>
+      <c r="A203" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B203" s="9">
         <f>IF(A203="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A203,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C203" s="4" t="n"/>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D203" s="4" t="n"/>
-      <c r="E203" s="4" t="n"/>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F203" s="11" t="n"/>
-      <c r="G203" s="4" t="n"/>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H203" s="11" t="n"/>
       <c r="I203" s="11" t="n"/>
       <c r="J203" s="9">
@@ -5544,16 +8372,30 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="11" t="n"/>
+      <c r="A204" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B204" s="9">
         <f>IF(A204="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A204,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C204" s="4" t="n"/>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D204" s="4" t="n"/>
-      <c r="E204" s="4" t="n"/>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F204" s="11" t="n"/>
-      <c r="G204" s="4" t="n"/>
+      <c r="G204" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H204" s="11" t="n"/>
       <c r="I204" s="11" t="n"/>
       <c r="J204" s="9">
@@ -5567,16 +8409,30 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="11" t="n"/>
+      <c r="A205" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B205" s="9">
         <f>IF(A205="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A205,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C205" s="4" t="n"/>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D205" s="4" t="n"/>
-      <c r="E205" s="4" t="n"/>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F205" s="11" t="n"/>
-      <c r="G205" s="4" t="n"/>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H205" s="11" t="n"/>
       <c r="I205" s="11" t="n"/>
       <c r="J205" s="9">
@@ -5590,16 +8446,30 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="11" t="n"/>
+      <c r="A206" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B206" s="9">
         <f>IF(A206="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A206,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C206" s="4" t="n"/>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D206" s="4" t="n"/>
-      <c r="E206" s="4" t="n"/>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F206" s="11" t="n"/>
-      <c r="G206" s="4" t="n"/>
+      <c r="G206" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H206" s="11" t="n"/>
       <c r="I206" s="11" t="n"/>
       <c r="J206" s="9">
@@ -5613,16 +8483,30 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="11" t="n"/>
+      <c r="A207" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B207" s="9">
         <f>IF(A207="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A207,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C207" s="4" t="n"/>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D207" s="4" t="n"/>
-      <c r="E207" s="4" t="n"/>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F207" s="11" t="n"/>
-      <c r="G207" s="4" t="n"/>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H207" s="11" t="n"/>
       <c r="I207" s="11" t="n"/>
       <c r="J207" s="9">
@@ -5636,16 +8520,30 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="11" t="n"/>
+      <c r="A208" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B208" s="9">
         <f>IF(A208="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A208,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C208" s="4" t="n"/>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D208" s="4" t="n"/>
-      <c r="E208" s="4" t="n"/>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F208" s="11" t="n"/>
-      <c r="G208" s="4" t="n"/>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H208" s="11" t="n"/>
       <c r="I208" s="11" t="n"/>
       <c r="J208" s="9">
@@ -5659,16 +8557,30 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="11" t="n"/>
+      <c r="A209" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B209" s="9">
         <f>IF(A209="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A209,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C209" s="4" t="n"/>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D209" s="4" t="n"/>
-      <c r="E209" s="4" t="n"/>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F209" s="11" t="n"/>
-      <c r="G209" s="4" t="n"/>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H209" s="11" t="n"/>
       <c r="I209" s="11" t="n"/>
       <c r="J209" s="9">
@@ -5682,16 +8594,30 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="11" t="n"/>
+      <c r="A210" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B210" s="9">
         <f>IF(A210="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A210,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C210" s="4" t="n"/>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D210" s="4" t="n"/>
-      <c r="E210" s="4" t="n"/>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F210" s="11" t="n"/>
-      <c r="G210" s="4" t="n"/>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H210" s="11" t="n"/>
       <c r="I210" s="11" t="n"/>
       <c r="J210" s="9">
@@ -5705,16 +8631,30 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="11" t="n"/>
+      <c r="A211" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B211" s="9">
         <f>IF(A211="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A211,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C211" s="4" t="n"/>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D211" s="4" t="n"/>
-      <c r="E211" s="4" t="n"/>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F211" s="11" t="n"/>
-      <c r="G211" s="4" t="n"/>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H211" s="11" t="n"/>
       <c r="I211" s="11" t="n"/>
       <c r="J211" s="9">
@@ -5728,16 +8668,30 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="11" t="n"/>
+      <c r="A212" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B212" s="9">
         <f>IF(A212="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A212,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C212" s="4" t="n"/>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D212" s="4" t="n"/>
-      <c r="E212" s="4" t="n"/>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F212" s="11" t="n"/>
-      <c r="G212" s="4" t="n"/>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H212" s="11" t="n"/>
       <c r="I212" s="11" t="n"/>
       <c r="J212" s="9">
@@ -5751,16 +8705,30 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="11" t="n"/>
+      <c r="A213" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B213" s="9">
         <f>IF(A213="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A213,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C213" s="4" t="n"/>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D213" s="4" t="n"/>
-      <c r="E213" s="4" t="n"/>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F213" s="11" t="n"/>
-      <c r="G213" s="4" t="n"/>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H213" s="11" t="n"/>
       <c r="I213" s="11" t="n"/>
       <c r="J213" s="9">
@@ -5774,16 +8742,30 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="11" t="n"/>
+      <c r="A214" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="B214" s="9">
         <f>IF(A214="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A214,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C214" s="4" t="n"/>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>6A D1</t>
+        </is>
+      </c>
       <c r="D214" s="4" t="n"/>
-      <c r="E214" s="4" t="n"/>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F214" s="11" t="n"/>
-      <c r="G214" s="4" t="n"/>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H214" s="11" t="n"/>
       <c r="I214" s="11" t="n"/>
       <c r="J214" s="9">
@@ -5797,16 +8779,30 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="11" t="n"/>
+      <c r="A215" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B215" s="9">
         <f>IF(A215="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A215,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C215" s="4" t="n"/>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D215" s="4" t="n"/>
-      <c r="E215" s="4" t="n"/>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>Winner G1</t>
+        </is>
+      </c>
       <c r="F215" s="11" t="n"/>
-      <c r="G215" s="4" t="n"/>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>Winner G2</t>
+        </is>
+      </c>
       <c r="H215" s="11" t="n"/>
       <c r="I215" s="11" t="n"/>
       <c r="J215" s="9">
@@ -5820,16 +8816,30 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="11" t="n"/>
+      <c r="A216" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B216" s="9">
         <f>IF(A216="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A216,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C216" s="4" t="n"/>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D216" s="4" t="n"/>
-      <c r="E216" s="4" t="n"/>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>Winner G3</t>
+        </is>
+      </c>
       <c r="F216" s="11" t="n"/>
-      <c r="G216" s="4" t="n"/>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>Winner G4</t>
+        </is>
+      </c>
       <c r="H216" s="11" t="n"/>
       <c r="I216" s="11" t="n"/>
       <c r="J216" s="9">
@@ -5843,16 +8853,30 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="11" t="n"/>
+      <c r="A217" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B217" s="9">
         <f>IF(A217="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A217,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C217" s="4" t="n"/>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D217" s="4" t="n"/>
-      <c r="E217" s="4" t="n"/>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>Winner G5</t>
+        </is>
+      </c>
       <c r="F217" s="11" t="n"/>
-      <c r="G217" s="4" t="n"/>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>Winner G6</t>
+        </is>
+      </c>
       <c r="H217" s="11" t="n"/>
       <c r="I217" s="11" t="n"/>
       <c r="J217" s="9">
@@ -5866,16 +8890,30 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="11" t="n"/>
+      <c r="A218" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B218" s="9">
         <f>IF(A218="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A218,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C218" s="4" t="n"/>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D218" s="4" t="n"/>
-      <c r="E218" s="4" t="n"/>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>Winner G7</t>
+        </is>
+      </c>
       <c r="F218" s="11" t="n"/>
-      <c r="G218" s="4" t="n"/>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t>Winner G8</t>
+        </is>
+      </c>
       <c r="H218" s="11" t="n"/>
       <c r="I218" s="11" t="n"/>
       <c r="J218" s="9">
@@ -5889,16 +8927,30 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="11" t="n"/>
+      <c r="A219" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B219" s="9">
         <f>IF(A219="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A219,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C219" s="4" t="n"/>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D219" s="4" t="n"/>
-      <c r="E219" s="4" t="n"/>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>Winner G9</t>
+        </is>
+      </c>
       <c r="F219" s="11" t="n"/>
-      <c r="G219" s="4" t="n"/>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>Winner G10</t>
+        </is>
+      </c>
       <c r="H219" s="11" t="n"/>
       <c r="I219" s="11" t="n"/>
       <c r="J219" s="9">
@@ -5912,16 +8964,30 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="11" t="n"/>
+      <c r="A220" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B220" s="9">
         <f>IF(A220="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A220,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C220" s="4" t="n"/>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D220" s="4" t="n"/>
-      <c r="E220" s="4" t="n"/>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>Winner G33</t>
+        </is>
+      </c>
       <c r="F220" s="11" t="n"/>
-      <c r="G220" s="4" t="n"/>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>Winner G34</t>
+        </is>
+      </c>
       <c r="H220" s="11" t="n"/>
       <c r="I220" s="11" t="n"/>
       <c r="J220" s="9">
@@ -5935,16 +9001,30 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="11" t="n"/>
+      <c r="A221" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B221" s="9">
         <f>IF(A221="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A221,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C221" s="4" t="n"/>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D221" s="4" t="n"/>
-      <c r="E221" s="4" t="n"/>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>Winner G35</t>
+        </is>
+      </c>
       <c r="F221" s="11" t="n"/>
-      <c r="G221" s="4" t="n"/>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>Winner G36</t>
+        </is>
+      </c>
       <c r="H221" s="11" t="n"/>
       <c r="I221" s="11" t="n"/>
       <c r="J221" s="9">
@@ -5958,16 +9038,30 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="11" t="n"/>
+      <c r="A222" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B222" s="9">
         <f>IF(A222="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A222,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C222" s="4" t="n"/>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D222" s="4" t="n"/>
-      <c r="E222" s="4" t="n"/>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>Winner G37</t>
+        </is>
+      </c>
       <c r="F222" s="11" t="n"/>
-      <c r="G222" s="4" t="n"/>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>Winner G38</t>
+        </is>
+      </c>
       <c r="H222" s="11" t="n"/>
       <c r="I222" s="11" t="n"/>
       <c r="J222" s="9">
@@ -5981,16 +9075,30 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="11" t="n"/>
+      <c r="A223" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B223" s="9">
         <f>IF(A223="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A223,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C223" s="4" t="n"/>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D223" s="4" t="n"/>
-      <c r="E223" s="4" t="n"/>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>Winner G39</t>
+        </is>
+      </c>
       <c r="F223" s="11" t="n"/>
-      <c r="G223" s="4" t="n"/>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>Winner G40</t>
+        </is>
+      </c>
       <c r="H223" s="11" t="n"/>
       <c r="I223" s="11" t="n"/>
       <c r="J223" s="9">
@@ -6004,16 +9112,30 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="11" t="n"/>
+      <c r="A224" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B224" s="9">
         <f>IF(A224="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A224,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C224" s="4" t="n"/>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D224" s="4" t="n"/>
-      <c r="E224" s="4" t="n"/>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>Winner G49</t>
+        </is>
+      </c>
       <c r="F224" s="11" t="n"/>
-      <c r="G224" s="4" t="n"/>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>Winner G50</t>
+        </is>
+      </c>
       <c r="H224" s="11" t="n"/>
       <c r="I224" s="11" t="n"/>
       <c r="J224" s="9">
@@ -6027,16 +9149,30 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="11" t="n"/>
+      <c r="A225" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B225" s="9">
         <f>IF(A225="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A225,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C225" s="4" t="n"/>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D225" s="4" t="n"/>
-      <c r="E225" s="4" t="n"/>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>Winner G51</t>
+        </is>
+      </c>
       <c r="F225" s="11" t="n"/>
-      <c r="G225" s="4" t="n"/>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>Winner G52</t>
+        </is>
+      </c>
       <c r="H225" s="11" t="n"/>
       <c r="I225" s="11" t="n"/>
       <c r="J225" s="9">
@@ -6050,16 +9186,30 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="11" t="n"/>
+      <c r="A226" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="B226" s="9">
         <f>IF(A226="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A226,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C226" s="4" t="n"/>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D226" s="4" t="n"/>
-      <c r="E226" s="4" t="n"/>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>Winner G29</t>
+        </is>
+      </c>
       <c r="F226" s="11" t="n"/>
-      <c r="G226" s="4" t="n"/>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>Winner G30</t>
+        </is>
+      </c>
       <c r="H226" s="11" t="n"/>
       <c r="I226" s="11" t="n"/>
       <c r="J226" s="9">
@@ -6073,16 +9223,30 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="11" t="n"/>
+      <c r="A227" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B227" s="9">
         <f>IF(A227="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A227,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C227" s="4" t="n"/>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D227" s="4" t="n"/>
-      <c r="E227" s="4" t="n"/>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>Winner G41</t>
+        </is>
+      </c>
       <c r="F227" s="11" t="n"/>
-      <c r="G227" s="4" t="n"/>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>Winner G42</t>
+        </is>
+      </c>
       <c r="H227" s="11" t="n"/>
       <c r="I227" s="11" t="n"/>
       <c r="J227" s="9">
@@ -6096,16 +9260,30 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="11" t="n"/>
+      <c r="A228" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B228" s="9">
         <f>IF(A228="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A228,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C228" s="4" t="n"/>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D228" s="4" t="n"/>
-      <c r="E228" s="4" t="n"/>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>Winner G43</t>
+        </is>
+      </c>
       <c r="F228" s="11" t="n"/>
-      <c r="G228" s="4" t="n"/>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>Winner G44</t>
+        </is>
+      </c>
       <c r="H228" s="11" t="n"/>
       <c r="I228" s="11" t="n"/>
       <c r="J228" s="9">
@@ -6119,16 +9297,30 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="11" t="n"/>
+      <c r="A229" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B229" s="9">
         <f>IF(A229="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A229,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C229" s="4" t="n"/>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D229" s="4" t="n"/>
-      <c r="E229" s="4" t="n"/>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>Winner G45</t>
+        </is>
+      </c>
       <c r="F229" s="11" t="n"/>
-      <c r="G229" s="4" t="n"/>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>Winner G46</t>
+        </is>
+      </c>
       <c r="H229" s="11" t="n"/>
       <c r="I229" s="11" t="n"/>
       <c r="J229" s="9">
@@ -6142,16 +9334,30 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="11" t="n"/>
+      <c r="A230" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="B230" s="9">
         <f>IF(A230="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A230,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C230" s="4" t="n"/>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D230" s="4" t="n"/>
-      <c r="E230" s="4" t="n"/>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>Winner G47</t>
+        </is>
+      </c>
       <c r="F230" s="11" t="n"/>
-      <c r="G230" s="4" t="n"/>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>Winner G48</t>
+        </is>
+      </c>
       <c r="H230" s="11" t="n"/>
       <c r="I230" s="11" t="n"/>
       <c r="J230" s="9">
@@ -6165,16 +9371,30 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="11" t="n"/>
+      <c r="A231" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B231" s="9">
         <f>IF(A231="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A231,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C231" s="4" t="n"/>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D231" s="4" t="n"/>
-      <c r="E231" s="4" t="n"/>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t>Winner G53</t>
+        </is>
+      </c>
       <c r="F231" s="11" t="n"/>
-      <c r="G231" s="4" t="n"/>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>Winner G54</t>
+        </is>
+      </c>
       <c r="H231" s="11" t="n"/>
       <c r="I231" s="11" t="n"/>
       <c r="J231" s="9">
@@ -6188,16 +9408,30 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="11" t="n"/>
+      <c r="A232" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="B232" s="9">
         <f>IF(A232="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A232,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C232" s="4" t="n"/>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D232" s="4" t="n"/>
-      <c r="E232" s="4" t="n"/>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>Winner G55</t>
+        </is>
+      </c>
       <c r="F232" s="11" t="n"/>
-      <c r="G232" s="4" t="n"/>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>Winner G56</t>
+        </is>
+      </c>
       <c r="H232" s="11" t="n"/>
       <c r="I232" s="11" t="n"/>
       <c r="J232" s="9">
@@ -6211,16 +9445,30 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="11" t="n"/>
+      <c r="A233" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B233" s="9">
         <f>IF(A233="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A233,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C233" s="4" t="n"/>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D233" s="4" t="n"/>
-      <c r="E233" s="4" t="n"/>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>Winner G57</t>
+        </is>
+      </c>
       <c r="F233" s="11" t="n"/>
-      <c r="G233" s="4" t="n"/>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>Winner G58</t>
+        </is>
+      </c>
       <c r="H233" s="11" t="n"/>
       <c r="I233" s="11" t="n"/>
       <c r="J233" s="9">
@@ -6234,16 +9482,30 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="11" t="n"/>
+      <c r="A234" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="B234" s="9">
         <f>IF(A234="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A234,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C234" s="4" t="n"/>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D234" s="4" t="n"/>
-      <c r="E234" s="4" t="n"/>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>Winner G59</t>
+        </is>
+      </c>
       <c r="F234" s="11" t="n"/>
-      <c r="G234" s="4" t="n"/>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>Winner G60</t>
+        </is>
+      </c>
       <c r="H234" s="11" t="n"/>
       <c r="I234" s="11" t="n"/>
       <c r="J234" s="9">
@@ -6257,16 +9519,30 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="11" t="n"/>
+      <c r="A235" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="B235" s="9">
         <f>IF(A235="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A235,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C235" s="4" t="n"/>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>6A D2</t>
+        </is>
+      </c>
       <c r="D235" s="4" t="n"/>
-      <c r="E235" s="4" t="n"/>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>Winner G61</t>
+        </is>
+      </c>
       <c r="F235" s="11" t="n"/>
-      <c r="G235" s="4" t="n"/>
+      <c r="G235" s="4" t="inlineStr">
+        <is>
+          <t>Winner G62</t>
+        </is>
+      </c>
       <c r="H235" s="11" t="n"/>
       <c r="I235" s="11" t="n"/>
       <c r="J235" s="9">

--- a/season/2026/2026_season.xlsx
+++ b/season/2026/2026_season.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Games" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chapter Stats" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="By Classification" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lists" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Games" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Stats" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Classification" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Games'!$A$1:$L$801</definedName>
@@ -898,30 +898,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A2" s="11" t="n"/>
       <c r="B2" s="9">
         <f>IF(A2="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A2,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E2" s="4" t="n"/>
       <c r="F2" s="11" t="n"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G2" s="4" t="n"/>
       <c r="H2" s="11" t="n"/>
       <c r="I2" s="11" t="n"/>
       <c r="J2" s="9">
@@ -935,30 +921,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A3" s="11" t="n"/>
       <c r="B3" s="9">
         <f>IF(A3="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A3,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E3" s="4" t="n"/>
       <c r="F3" s="11" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G3" s="4" t="n"/>
       <c r="H3" s="11" t="n"/>
       <c r="I3" s="11" t="n"/>
       <c r="J3" s="9">
@@ -972,30 +944,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A4" s="11" t="n"/>
       <c r="B4" s="9">
         <f>IF(A4="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A4,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="n"/>
       <c r="F4" s="11" t="n"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="11" t="n"/>
       <c r="I4" s="11" t="n"/>
       <c r="J4" s="9">
@@ -1009,30 +967,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A5" s="11" t="n"/>
       <c r="B5" s="9">
         <f>IF(A5="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A5,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="n"/>
       <c r="F5" s="11" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G5" s="4" t="n"/>
       <c r="H5" s="11" t="n"/>
       <c r="I5" s="11" t="n"/>
       <c r="J5" s="9">
@@ -1046,30 +990,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A6" s="11" t="n"/>
       <c r="B6" s="9">
         <f>IF(A6="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A6,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Winner G17</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="n"/>
       <c r="F6" s="11" t="n"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Winner G18</t>
-        </is>
-      </c>
+      <c r="G6" s="4" t="n"/>
       <c r="H6" s="11" t="n"/>
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="9">
@@ -1083,30 +1013,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A7" s="11" t="n"/>
       <c r="B7" s="9">
         <f>IF(A7="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A7,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Winner G19</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="n"/>
       <c r="F7" s="11" t="n"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Winner G20</t>
-        </is>
-      </c>
+      <c r="G7" s="4" t="n"/>
       <c r="H7" s="11" t="n"/>
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="9">
@@ -1120,30 +1036,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A8" s="11" t="n"/>
       <c r="B8" s="9">
         <f>IF(A8="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A8,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="n"/>
       <c r="F8" s="11" t="n"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G8" s="4" t="n"/>
       <c r="H8" s="11" t="n"/>
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="9">
@@ -1157,30 +1059,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A9" s="11" t="n"/>
       <c r="B9" s="9">
         <f>IF(A9="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A9,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Winner G21</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="n"/>
       <c r="F9" s="11" t="n"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Winner G22</t>
-        </is>
-      </c>
+      <c r="G9" s="4" t="n"/>
       <c r="H9" s="11" t="n"/>
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="9">
@@ -1194,30 +1082,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A10" s="11" t="n"/>
       <c r="B10" s="9">
         <f>IF(A10="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A10,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Winner G23</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="n"/>
       <c r="F10" s="11" t="n"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Winner G24</t>
-        </is>
-      </c>
+      <c r="G10" s="4" t="n"/>
       <c r="H10" s="11" t="n"/>
       <c r="I10" s="11" t="n"/>
       <c r="J10" s="9">
@@ -1231,30 +1105,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A11" s="11" t="n"/>
       <c r="B11" s="9">
         <f>IF(A11="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A11,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Winner G25</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="n"/>
       <c r="F11" s="11" t="n"/>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Winner G26</t>
-        </is>
-      </c>
+      <c r="G11" s="4" t="n"/>
       <c r="H11" s="11" t="n"/>
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="9">
@@ -1268,30 +1128,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A12" s="11" t="n"/>
       <c r="B12" s="9">
         <f>IF(A12="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A12,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Winner G27</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="n"/>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Winner G28</t>
-        </is>
-      </c>
+      <c r="G12" s="4" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="9">
@@ -1305,30 +1151,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A13" s="11" t="n"/>
       <c r="B13" s="9">
         <f>IF(A13="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A13,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>1A D1</t>
-        </is>
-      </c>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="n"/>
       <c r="F13" s="11" t="n"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G13" s="4" t="n"/>
       <c r="H13" s="11" t="n"/>
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="9">
@@ -1342,30 +1174,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A14" s="11" t="n"/>
       <c r="B14" s="9">
         <f>IF(A14="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A14,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="n"/>
       <c r="F14" s="11" t="n"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G14" s="4" t="n"/>
       <c r="H14" s="11" t="n"/>
       <c r="I14" s="11" t="n"/>
       <c r="J14" s="9">
@@ -1379,30 +1197,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A15" s="11" t="n"/>
       <c r="B15" s="9">
         <f>IF(A15="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A15,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G15" s="4" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="9">
@@ -1416,30 +1220,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A16" s="11" t="n"/>
       <c r="B16" s="9">
         <f>IF(A16="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A16,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="n"/>
       <c r="F16" s="11" t="n"/>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G16" s="4" t="n"/>
       <c r="H16" s="11" t="n"/>
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="9">
@@ -1453,30 +1243,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A17" s="11" t="n"/>
       <c r="B17" s="9">
         <f>IF(A17="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A17,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="n"/>
       <c r="F17" s="11" t="n"/>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G17" s="4" t="n"/>
       <c r="H17" s="11" t="n"/>
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="9">
@@ -1490,30 +1266,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A18" s="11" t="n"/>
       <c r="B18" s="9">
         <f>IF(A18="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A18,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Winner G17</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="n"/>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Winner G18</t>
-        </is>
-      </c>
+      <c r="G18" s="4" t="n"/>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="9">
@@ -1527,30 +1289,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A19" s="11" t="n"/>
       <c r="B19" s="9">
         <f>IF(A19="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A19,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Winner G19</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="n"/>
       <c r="F19" s="11" t="n"/>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Winner G20</t>
-        </is>
-      </c>
+      <c r="G19" s="4" t="n"/>
       <c r="H19" s="11" t="n"/>
       <c r="I19" s="11" t="n"/>
       <c r="J19" s="9">
@@ -1564,30 +1312,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A20" s="11" t="n"/>
       <c r="B20" s="9">
         <f>IF(A20="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A20,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="n"/>
       <c r="F20" s="11" t="n"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G20" s="4" t="n"/>
       <c r="H20" s="11" t="n"/>
       <c r="I20" s="11" t="n"/>
       <c r="J20" s="9">
@@ -1601,30 +1335,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A21" s="11" t="n"/>
       <c r="B21" s="9">
         <f>IF(A21="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A21,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Winner G21</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="n"/>
       <c r="F21" s="11" t="n"/>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Winner G22</t>
-        </is>
-      </c>
+      <c r="G21" s="4" t="n"/>
       <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="9">
@@ -1638,30 +1358,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A22" s="11" t="n"/>
       <c r="B22" s="9">
         <f>IF(A22="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A22,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Winner G23</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="n"/>
       <c r="F22" s="11" t="n"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Winner G24</t>
-        </is>
-      </c>
+      <c r="G22" s="4" t="n"/>
       <c r="H22" s="11" t="n"/>
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="9">
@@ -1675,30 +1381,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A23" s="11" t="n"/>
       <c r="B23" s="9">
         <f>IF(A23="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A23,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Winner G25</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="n"/>
       <c r="F23" s="11" t="n"/>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Winner G26</t>
-        </is>
-      </c>
+      <c r="G23" s="4" t="n"/>
       <c r="H23" s="11" t="n"/>
       <c r="I23" s="11" t="n"/>
       <c r="J23" s="9">
@@ -1712,30 +1404,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A24" s="11" t="n"/>
       <c r="B24" s="9">
         <f>IF(A24="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A24,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Winner G27</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="n"/>
       <c r="F24" s="11" t="n"/>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Winner G28</t>
-        </is>
-      </c>
+      <c r="G24" s="4" t="n"/>
       <c r="H24" s="11" t="n"/>
       <c r="I24" s="11" t="n"/>
       <c r="J24" s="9">
@@ -1749,30 +1427,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A25" s="11" t="n"/>
       <c r="B25" s="9">
         <f>IF(A25="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A25,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>1A D2</t>
-        </is>
-      </c>
+      <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="n"/>
       <c r="F25" s="11" t="n"/>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G25" s="4" t="n"/>
       <c r="H25" s="11" t="n"/>
       <c r="I25" s="11" t="n"/>
       <c r="J25" s="9">
@@ -1786,30 +1450,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A26" s="11" t="n"/>
       <c r="B26" s="9">
         <f>IF(A26="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A26,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="n"/>
       <c r="F26" s="11" t="n"/>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G26" s="4" t="n"/>
       <c r="H26" s="11" t="n"/>
       <c r="I26" s="11" t="n"/>
       <c r="J26" s="9">
@@ -1823,30 +1473,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A27" s="11" t="n"/>
       <c r="B27" s="9">
         <f>IF(A27="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A27,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="n"/>
       <c r="F27" s="11" t="n"/>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G27" s="4" t="n"/>
       <c r="H27" s="11" t="n"/>
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="9">
@@ -1860,30 +1496,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A28" s="11" t="n"/>
       <c r="B28" s="9">
         <f>IF(A28="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A28,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="n"/>
       <c r="F28" s="11" t="n"/>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G28" s="4" t="n"/>
       <c r="H28" s="11" t="n"/>
       <c r="I28" s="11" t="n"/>
       <c r="J28" s="9">
@@ -1897,30 +1519,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A29" s="11" t="n"/>
       <c r="B29" s="9">
         <f>IF(A29="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A29,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="n"/>
       <c r="F29" s="11" t="n"/>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G29" s="4" t="n"/>
       <c r="H29" s="11" t="n"/>
       <c r="I29" s="11" t="n"/>
       <c r="J29" s="9">
@@ -1934,30 +1542,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A30" s="11" t="n"/>
       <c r="B30" s="9">
         <f>IF(A30="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A30,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="n"/>
       <c r="F30" s="11" t="n"/>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G30" s="4" t="n"/>
       <c r="H30" s="11" t="n"/>
       <c r="I30" s="11" t="n"/>
       <c r="J30" s="9">
@@ -1971,30 +1565,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A31" s="11" t="n"/>
       <c r="B31" s="9">
         <f>IF(A31="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A31,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="n"/>
       <c r="F31" s="11" t="n"/>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G31" s="4" t="n"/>
       <c r="H31" s="11" t="n"/>
       <c r="I31" s="11" t="n"/>
       <c r="J31" s="9">
@@ -2008,30 +1588,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A32" s="11" t="n"/>
       <c r="B32" s="9">
         <f>IF(A32="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A32,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="n"/>
       <c r="F32" s="11" t="n"/>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G32" s="4" t="n"/>
       <c r="H32" s="11" t="n"/>
       <c r="I32" s="11" t="n"/>
       <c r="J32" s="9">
@@ -2045,30 +1611,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A33" s="11" t="n"/>
       <c r="B33" s="9">
         <f>IF(A33="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A33,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="n"/>
       <c r="F33" s="11" t="n"/>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G33" s="4" t="n"/>
       <c r="H33" s="11" t="n"/>
       <c r="I33" s="11" t="n"/>
       <c r="J33" s="9">
@@ -2082,30 +1634,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A34" s="11" t="n"/>
       <c r="B34" s="9">
         <f>IF(A34="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A34,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="n"/>
       <c r="F34" s="11" t="n"/>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G34" s="4" t="n"/>
       <c r="H34" s="11" t="n"/>
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="9">
@@ -2119,30 +1657,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A35" s="11" t="n"/>
       <c r="B35" s="9">
         <f>IF(A35="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A35,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="n"/>
       <c r="F35" s="11" t="n"/>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G35" s="4" t="n"/>
       <c r="H35" s="11" t="n"/>
       <c r="I35" s="11" t="n"/>
       <c r="J35" s="9">
@@ -2156,30 +1680,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A36" s="11" t="n"/>
       <c r="B36" s="9">
         <f>IF(A36="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A36,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C36" s="4" t="n"/>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="n"/>
       <c r="F36" s="11" t="n"/>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G36" s="4" t="n"/>
       <c r="H36" s="11" t="n"/>
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="9">
@@ -2193,30 +1703,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A37" s="11" t="n"/>
       <c r="B37" s="9">
         <f>IF(A37="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A37,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="n"/>
       <c r="F37" s="11" t="n"/>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G37" s="4" t="n"/>
       <c r="H37" s="11" t="n"/>
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="9">
@@ -2230,30 +1726,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A38" s="11" t="n"/>
       <c r="B38" s="9">
         <f>IF(A38="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A38,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C38" s="4" t="n"/>
       <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="n"/>
       <c r="F38" s="11" t="n"/>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G38" s="4" t="n"/>
       <c r="H38" s="11" t="n"/>
       <c r="I38" s="11" t="n"/>
       <c r="J38" s="9">
@@ -2267,30 +1749,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A39" s="11" t="n"/>
       <c r="B39" s="9">
         <f>IF(A39="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A39,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="n"/>
       <c r="F39" s="11" t="n"/>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G39" s="4" t="n"/>
       <c r="H39" s="11" t="n"/>
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="9">
@@ -2304,30 +1772,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A40" s="11" t="n"/>
       <c r="B40" s="9">
         <f>IF(A40="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A40,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="n"/>
       <c r="F40" s="11" t="n"/>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G40" s="4" t="n"/>
       <c r="H40" s="11" t="n"/>
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="9">
@@ -2341,30 +1795,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A41" s="11" t="n"/>
       <c r="B41" s="9">
         <f>IF(A41="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A41,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="n"/>
       <c r="F41" s="11" t="n"/>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G41" s="4" t="n"/>
       <c r="H41" s="11" t="n"/>
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="9">
@@ -2378,30 +1818,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A42" s="11" t="n"/>
       <c r="B42" s="9">
         <f>IF(A42="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A42,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="n"/>
       <c r="F42" s="11" t="n"/>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G42" s="4" t="n"/>
       <c r="H42" s="11" t="n"/>
       <c r="I42" s="11" t="n"/>
       <c r="J42" s="9">
@@ -2415,30 +1841,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A43" s="11" t="n"/>
       <c r="B43" s="9">
         <f>IF(A43="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A43,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="n"/>
       <c r="F43" s="11" t="n"/>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G43" s="4" t="n"/>
       <c r="H43" s="11" t="n"/>
       <c r="I43" s="11" t="n"/>
       <c r="J43" s="9">
@@ -2452,30 +1864,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A44" s="11" t="n"/>
       <c r="B44" s="9">
         <f>IF(A44="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A44,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="n"/>
       <c r="F44" s="11" t="n"/>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G44" s="4" t="n"/>
       <c r="H44" s="11" t="n"/>
       <c r="I44" s="11" t="n"/>
       <c r="J44" s="9">
@@ -2489,30 +1887,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A45" s="11" t="n"/>
       <c r="B45" s="9">
         <f>IF(A45="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A45,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="n"/>
       <c r="F45" s="11" t="n"/>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G45" s="4" t="n"/>
       <c r="H45" s="11" t="n"/>
       <c r="I45" s="11" t="n"/>
       <c r="J45" s="9">
@@ -2526,30 +1910,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="A46" s="11" t="n"/>
       <c r="B46" s="9">
         <f>IF(A46="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A46,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>2A D1</t>
-        </is>
-      </c>
+      <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="n"/>
       <c r="F46" s="11" t="n"/>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G46" s="4" t="n"/>
       <c r="H46" s="11" t="n"/>
       <c r="I46" s="11" t="n"/>
       <c r="J46" s="9">
@@ -2563,30 +1933,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A47" s="11" t="n"/>
       <c r="B47" s="9">
         <f>IF(A47="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A47,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="n"/>
       <c r="F47" s="11" t="n"/>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G47" s="4" t="n"/>
       <c r="H47" s="11" t="n"/>
       <c r="I47" s="11" t="n"/>
       <c r="J47" s="9">
@@ -2600,30 +1956,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A48" s="11" t="n"/>
       <c r="B48" s="9">
         <f>IF(A48="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A48,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="n"/>
       <c r="F48" s="11" t="n"/>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G48" s="4" t="n"/>
       <c r="H48" s="11" t="n"/>
       <c r="I48" s="11" t="n"/>
       <c r="J48" s="9">
@@ -2637,30 +1979,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A49" s="11" t="n"/>
       <c r="B49" s="9">
         <f>IF(A49="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A49,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="n"/>
       <c r="F49" s="11" t="n"/>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G49" s="4" t="n"/>
       <c r="H49" s="11" t="n"/>
       <c r="I49" s="11" t="n"/>
       <c r="J49" s="9">
@@ -2674,30 +2002,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A50" s="11" t="n"/>
       <c r="B50" s="9">
         <f>IF(A50="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A50,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="n"/>
       <c r="F50" s="11" t="n"/>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G50" s="4" t="n"/>
       <c r="H50" s="11" t="n"/>
       <c r="I50" s="11" t="n"/>
       <c r="J50" s="9">
@@ -2711,30 +2025,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A51" s="11" t="n"/>
       <c r="B51" s="9">
         <f>IF(A51="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A51,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="n"/>
       <c r="F51" s="11" t="n"/>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G51" s="4" t="n"/>
       <c r="H51" s="11" t="n"/>
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="9">
@@ -2748,30 +2048,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A52" s="11" t="n"/>
       <c r="B52" s="9">
         <f>IF(A52="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A52,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="n"/>
       <c r="F52" s="11" t="n"/>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G52" s="4" t="n"/>
       <c r="H52" s="11" t="n"/>
       <c r="I52" s="11" t="n"/>
       <c r="J52" s="9">
@@ -2785,30 +2071,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A53" s="11" t="n"/>
       <c r="B53" s="9">
         <f>IF(A53="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A53,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="n"/>
       <c r="F53" s="11" t="n"/>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G53" s="4" t="n"/>
       <c r="H53" s="11" t="n"/>
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="9">
@@ -2822,30 +2094,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A54" s="11" t="n"/>
       <c r="B54" s="9">
         <f>IF(A54="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A54,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="n"/>
       <c r="F54" s="11" t="n"/>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G54" s="4" t="n"/>
       <c r="H54" s="11" t="n"/>
       <c r="I54" s="11" t="n"/>
       <c r="J54" s="9">
@@ -2859,30 +2117,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A55" s="11" t="n"/>
       <c r="B55" s="9">
         <f>IF(A55="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A55,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="n"/>
       <c r="F55" s="11" t="n"/>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G55" s="4" t="n"/>
       <c r="H55" s="11" t="n"/>
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="9">
@@ -2896,30 +2140,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A56" s="11" t="n"/>
       <c r="B56" s="9">
         <f>IF(A56="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A56,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="n"/>
       <c r="F56" s="11" t="n"/>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G56" s="4" t="n"/>
       <c r="H56" s="11" t="n"/>
       <c r="I56" s="11" t="n"/>
       <c r="J56" s="9">
@@ -2933,30 +2163,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A57" s="11" t="n"/>
       <c r="B57" s="9">
         <f>IF(A57="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A57,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="n"/>
       <c r="F57" s="11" t="n"/>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G57" s="4" t="n"/>
       <c r="H57" s="11" t="n"/>
       <c r="I57" s="11" t="n"/>
       <c r="J57" s="9">
@@ -2970,30 +2186,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A58" s="11" t="n"/>
       <c r="B58" s="9">
         <f>IF(A58="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A58,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="n"/>
       <c r="F58" s="11" t="n"/>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G58" s="4" t="n"/>
       <c r="H58" s="11" t="n"/>
       <c r="I58" s="11" t="n"/>
       <c r="J58" s="9">
@@ -3007,30 +2209,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A59" s="11" t="n"/>
       <c r="B59" s="9">
         <f>IF(A59="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A59,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="n"/>
       <c r="F59" s="11" t="n"/>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G59" s="4" t="n"/>
       <c r="H59" s="11" t="n"/>
       <c r="I59" s="11" t="n"/>
       <c r="J59" s="9">
@@ -3044,30 +2232,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A60" s="11" t="n"/>
       <c r="B60" s="9">
         <f>IF(A60="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A60,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="n"/>
       <c r="F60" s="11" t="n"/>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G60" s="4" t="n"/>
       <c r="H60" s="11" t="n"/>
       <c r="I60" s="11" t="n"/>
       <c r="J60" s="9">
@@ -3081,30 +2255,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A61" s="11" t="n"/>
       <c r="B61" s="9">
         <f>IF(A61="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A61,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="n"/>
       <c r="F61" s="11" t="n"/>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G61" s="4" t="n"/>
       <c r="H61" s="11" t="n"/>
       <c r="I61" s="11" t="n"/>
       <c r="J61" s="9">
@@ -3118,30 +2278,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A62" s="11" t="n"/>
       <c r="B62" s="9">
         <f>IF(A62="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A62,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="n"/>
       <c r="F62" s="11" t="n"/>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G62" s="4" t="n"/>
       <c r="H62" s="11" t="n"/>
       <c r="I62" s="11" t="n"/>
       <c r="J62" s="9">
@@ -3155,30 +2301,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A63" s="11" t="n"/>
       <c r="B63" s="9">
         <f>IF(A63="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A63,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="n"/>
       <c r="F63" s="11" t="n"/>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G63" s="4" t="n"/>
       <c r="H63" s="11" t="n"/>
       <c r="I63" s="11" t="n"/>
       <c r="J63" s="9">
@@ -3192,30 +2324,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A64" s="11" t="n"/>
       <c r="B64" s="9">
         <f>IF(A64="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A64,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C64" s="4" t="n"/>
       <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="n"/>
       <c r="F64" s="11" t="n"/>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G64" s="4" t="n"/>
       <c r="H64" s="11" t="n"/>
       <c r="I64" s="11" t="n"/>
       <c r="J64" s="9">
@@ -3229,30 +2347,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A65" s="11" t="n"/>
       <c r="B65" s="9">
         <f>IF(A65="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A65,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="n"/>
       <c r="F65" s="11" t="n"/>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G65" s="4" t="n"/>
       <c r="H65" s="11" t="n"/>
       <c r="I65" s="11" t="n"/>
       <c r="J65" s="9">
@@ -3266,30 +2370,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A66" s="11" t="n"/>
       <c r="B66" s="9">
         <f>IF(A66="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A66,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C66" s="4" t="n"/>
       <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="n"/>
       <c r="F66" s="11" t="n"/>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G66" s="4" t="n"/>
       <c r="H66" s="11" t="n"/>
       <c r="I66" s="11" t="n"/>
       <c r="J66" s="9">
@@ -3303,30 +2393,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A67" s="11" t="n"/>
       <c r="B67" s="9">
         <f>IF(A67="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A67,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>2A D2</t>
-        </is>
-      </c>
+      <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="n"/>
       <c r="F67" s="11" t="n"/>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G67" s="4" t="n"/>
       <c r="H67" s="11" t="n"/>
       <c r="I67" s="11" t="n"/>
       <c r="J67" s="9">
@@ -3340,30 +2416,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A68" s="11" t="n"/>
       <c r="B68" s="9">
         <f>IF(A68="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A68,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="n"/>
       <c r="F68" s="11" t="n"/>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G68" s="4" t="n"/>
       <c r="H68" s="11" t="n"/>
       <c r="I68" s="11" t="n"/>
       <c r="J68" s="9">
@@ -3377,30 +2439,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A69" s="11" t="n"/>
       <c r="B69" s="9">
         <f>IF(A69="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A69,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C69" s="4" t="n"/>
       <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="n"/>
       <c r="F69" s="11" t="n"/>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G69" s="4" t="n"/>
       <c r="H69" s="11" t="n"/>
       <c r="I69" s="11" t="n"/>
       <c r="J69" s="9">
@@ -3414,30 +2462,16 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A70" s="11" t="n"/>
       <c r="B70" s="9">
         <f>IF(A70="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A70,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="n"/>
       <c r="F70" s="11" t="n"/>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G70" s="4" t="n"/>
       <c r="H70" s="11" t="n"/>
       <c r="I70" s="11" t="n"/>
       <c r="J70" s="9">
@@ -3451,30 +2485,16 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A71" s="11" t="n"/>
       <c r="B71" s="9">
         <f>IF(A71="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A71,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="n"/>
       <c r="F71" s="11" t="n"/>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G71" s="4" t="n"/>
       <c r="H71" s="11" t="n"/>
       <c r="I71" s="11" t="n"/>
       <c r="J71" s="9">
@@ -3488,30 +2508,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A72" s="11" t="n"/>
       <c r="B72" s="9">
         <f>IF(A72="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A72,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="n"/>
       <c r="F72" s="11" t="n"/>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G72" s="4" t="n"/>
       <c r="H72" s="11" t="n"/>
       <c r="I72" s="11" t="n"/>
       <c r="J72" s="9">
@@ -3525,30 +2531,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A73" s="11" t="n"/>
       <c r="B73" s="9">
         <f>IF(A73="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A73,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="n"/>
       <c r="F73" s="11" t="n"/>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G73" s="4" t="n"/>
       <c r="H73" s="11" t="n"/>
       <c r="I73" s="11" t="n"/>
       <c r="J73" s="9">
@@ -3562,30 +2554,16 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A74" s="11" t="n"/>
       <c r="B74" s="9">
         <f>IF(A74="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A74,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="n"/>
       <c r="F74" s="11" t="n"/>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G74" s="4" t="n"/>
       <c r="H74" s="11" t="n"/>
       <c r="I74" s="11" t="n"/>
       <c r="J74" s="9">
@@ -3599,30 +2577,16 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A75" s="11" t="n"/>
       <c r="B75" s="9">
         <f>IF(A75="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A75,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="n"/>
       <c r="F75" s="11" t="n"/>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G75" s="4" t="n"/>
       <c r="H75" s="11" t="n"/>
       <c r="I75" s="11" t="n"/>
       <c r="J75" s="9">
@@ -3636,30 +2600,16 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A76" s="11" t="n"/>
       <c r="B76" s="9">
         <f>IF(A76="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A76,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C76" s="4" t="n"/>
       <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="n"/>
       <c r="F76" s="11" t="n"/>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G76" s="4" t="n"/>
       <c r="H76" s="11" t="n"/>
       <c r="I76" s="11" t="n"/>
       <c r="J76" s="9">
@@ -3673,30 +2623,16 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A77" s="11" t="n"/>
       <c r="B77" s="9">
         <f>IF(A77="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A77,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C77" s="4" t="n"/>
       <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="n"/>
       <c r="F77" s="11" t="n"/>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G77" s="4" t="n"/>
       <c r="H77" s="11" t="n"/>
       <c r="I77" s="11" t="n"/>
       <c r="J77" s="9">
@@ -3710,30 +2646,16 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A78" s="11" t="n"/>
       <c r="B78" s="9">
         <f>IF(A78="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A78,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C78" s="4" t="n"/>
       <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="n"/>
       <c r="F78" s="11" t="n"/>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G78" s="4" t="n"/>
       <c r="H78" s="11" t="n"/>
       <c r="I78" s="11" t="n"/>
       <c r="J78" s="9">
@@ -3747,30 +2669,16 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A79" s="11" t="n"/>
       <c r="B79" s="9">
         <f>IF(A79="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A79,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C79" s="4" t="n"/>
       <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="n"/>
       <c r="F79" s="11" t="n"/>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G79" s="4" t="n"/>
       <c r="H79" s="11" t="n"/>
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="9">
@@ -3784,30 +2692,16 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A80" s="11" t="n"/>
       <c r="B80" s="9">
         <f>IF(A80="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A80,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C80" s="4" t="n"/>
       <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="n"/>
       <c r="F80" s="11" t="n"/>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G80" s="4" t="n"/>
       <c r="H80" s="11" t="n"/>
       <c r="I80" s="11" t="n"/>
       <c r="J80" s="9">
@@ -3821,30 +2715,16 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A81" s="11" t="n"/>
       <c r="B81" s="9">
         <f>IF(A81="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A81,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C81" s="4" t="n"/>
       <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="n"/>
       <c r="F81" s="11" t="n"/>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G81" s="4" t="n"/>
       <c r="H81" s="11" t="n"/>
       <c r="I81" s="11" t="n"/>
       <c r="J81" s="9">
@@ -3858,30 +2738,16 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A82" s="11" t="n"/>
       <c r="B82" s="9">
         <f>IF(A82="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A82,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C82" s="4" t="n"/>
       <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="n"/>
       <c r="F82" s="11" t="n"/>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G82" s="4" t="n"/>
       <c r="H82" s="11" t="n"/>
       <c r="I82" s="11" t="n"/>
       <c r="J82" s="9">
@@ -3895,30 +2761,16 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A83" s="11" t="n"/>
       <c r="B83" s="9">
         <f>IF(A83="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A83,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C83" s="4" t="n"/>
       <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="n"/>
       <c r="F83" s="11" t="n"/>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G83" s="4" t="n"/>
       <c r="H83" s="11" t="n"/>
       <c r="I83" s="11" t="n"/>
       <c r="J83" s="9">
@@ -3932,30 +2784,16 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A84" s="11" t="n"/>
       <c r="B84" s="9">
         <f>IF(A84="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A84,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C84" s="4" t="n"/>
       <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="n"/>
       <c r="F84" s="11" t="n"/>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G84" s="4" t="n"/>
       <c r="H84" s="11" t="n"/>
       <c r="I84" s="11" t="n"/>
       <c r="J84" s="9">
@@ -3969,30 +2807,16 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A85" s="11" t="n"/>
       <c r="B85" s="9">
         <f>IF(A85="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A85,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C85" s="4" t="n"/>
       <c r="D85" s="4" t="n"/>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="n"/>
       <c r="F85" s="11" t="n"/>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G85" s="4" t="n"/>
       <c r="H85" s="11" t="n"/>
       <c r="I85" s="11" t="n"/>
       <c r="J85" s="9">
@@ -4006,30 +2830,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A86" s="11" t="n"/>
       <c r="B86" s="9">
         <f>IF(A86="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A86,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C86" s="4" t="n"/>
       <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="n"/>
       <c r="F86" s="11" t="n"/>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G86" s="4" t="n"/>
       <c r="H86" s="11" t="n"/>
       <c r="I86" s="11" t="n"/>
       <c r="J86" s="9">
@@ -4043,30 +2853,16 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A87" s="11" t="n"/>
       <c r="B87" s="9">
         <f>IF(A87="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A87,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C87" s="4" t="n"/>
       <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="n"/>
       <c r="F87" s="11" t="n"/>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G87" s="4" t="n"/>
       <c r="H87" s="11" t="n"/>
       <c r="I87" s="11" t="n"/>
       <c r="J87" s="9">
@@ -4080,30 +2876,16 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="A88" s="11" t="n"/>
       <c r="B88" s="9">
         <f>IF(A88="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A88,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>3A D1</t>
-        </is>
-      </c>
+      <c r="C88" s="4" t="n"/>
       <c r="D88" s="4" t="n"/>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="n"/>
       <c r="F88" s="11" t="n"/>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G88" s="4" t="n"/>
       <c r="H88" s="11" t="n"/>
       <c r="I88" s="11" t="n"/>
       <c r="J88" s="9">
@@ -4117,30 +2899,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A89" s="11" t="n"/>
       <c r="B89" s="9">
         <f>IF(A89="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A89,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C89" s="4" t="n"/>
       <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="n"/>
       <c r="F89" s="11" t="n"/>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G89" s="4" t="n"/>
       <c r="H89" s="11" t="n"/>
       <c r="I89" s="11" t="n"/>
       <c r="J89" s="9">
@@ -4154,30 +2922,16 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A90" s="11" t="n"/>
       <c r="B90" s="9">
         <f>IF(A90="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A90,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C90" s="4" t="n"/>
       <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="n"/>
       <c r="F90" s="11" t="n"/>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G90" s="4" t="n"/>
       <c r="H90" s="11" t="n"/>
       <c r="I90" s="11" t="n"/>
       <c r="J90" s="9">
@@ -4191,30 +2945,16 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A91" s="11" t="n"/>
       <c r="B91" s="9">
         <f>IF(A91="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A91,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C91" s="4" t="n"/>
       <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="n"/>
       <c r="F91" s="11" t="n"/>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G91" s="4" t="n"/>
       <c r="H91" s="11" t="n"/>
       <c r="I91" s="11" t="n"/>
       <c r="J91" s="9">
@@ -4228,30 +2968,16 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A92" s="11" t="n"/>
       <c r="B92" s="9">
         <f>IF(A92="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A92,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C92" s="4" t="n"/>
       <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="n"/>
       <c r="F92" s="11" t="n"/>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G92" s="4" t="n"/>
       <c r="H92" s="11" t="n"/>
       <c r="I92" s="11" t="n"/>
       <c r="J92" s="9">
@@ -4265,30 +2991,16 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A93" s="11" t="n"/>
       <c r="B93" s="9">
         <f>IF(A93="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A93,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C93" s="4" t="n"/>
       <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="n"/>
       <c r="F93" s="11" t="n"/>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G93" s="4" t="n"/>
       <c r="H93" s="11" t="n"/>
       <c r="I93" s="11" t="n"/>
       <c r="J93" s="9">
@@ -4302,30 +3014,16 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A94" s="11" t="n"/>
       <c r="B94" s="9">
         <f>IF(A94="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A94,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C94" s="4" t="n"/>
       <c r="D94" s="4" t="n"/>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="n"/>
       <c r="F94" s="11" t="n"/>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G94" s="4" t="n"/>
       <c r="H94" s="11" t="n"/>
       <c r="I94" s="11" t="n"/>
       <c r="J94" s="9">
@@ -4339,30 +3037,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A95" s="11" t="n"/>
       <c r="B95" s="9">
         <f>IF(A95="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A95,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C95" s="4" t="n"/>
       <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="n"/>
       <c r="F95" s="11" t="n"/>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G95" s="4" t="n"/>
       <c r="H95" s="11" t="n"/>
       <c r="I95" s="11" t="n"/>
       <c r="J95" s="9">
@@ -4376,30 +3060,16 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A96" s="11" t="n"/>
       <c r="B96" s="9">
         <f>IF(A96="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A96,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C96" s="4" t="n"/>
       <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="n"/>
       <c r="F96" s="11" t="n"/>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G96" s="4" t="n"/>
       <c r="H96" s="11" t="n"/>
       <c r="I96" s="11" t="n"/>
       <c r="J96" s="9">
@@ -4413,30 +3083,16 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A97" s="11" t="n"/>
       <c r="B97" s="9">
         <f>IF(A97="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A97,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C97" s="4" t="n"/>
       <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="n"/>
       <c r="F97" s="11" t="n"/>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G97" s="4" t="n"/>
       <c r="H97" s="11" t="n"/>
       <c r="I97" s="11" t="n"/>
       <c r="J97" s="9">
@@ -4450,30 +3106,16 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A98" s="11" t="n"/>
       <c r="B98" s="9">
         <f>IF(A98="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A98,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C98" s="4" t="n"/>
       <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="n"/>
       <c r="F98" s="11" t="n"/>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G98" s="4" t="n"/>
       <c r="H98" s="11" t="n"/>
       <c r="I98" s="11" t="n"/>
       <c r="J98" s="9">
@@ -4487,30 +3129,16 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A99" s="11" t="n"/>
       <c r="B99" s="9">
         <f>IF(A99="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A99,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C99" s="4" t="n"/>
       <c r="D99" s="4" t="n"/>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="n"/>
       <c r="F99" s="11" t="n"/>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G99" s="4" t="n"/>
       <c r="H99" s="11" t="n"/>
       <c r="I99" s="11" t="n"/>
       <c r="J99" s="9">
@@ -4524,30 +3152,16 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A100" s="11" t="n"/>
       <c r="B100" s="9">
         <f>IF(A100="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A100,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C100" s="4" t="n"/>
       <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="n"/>
       <c r="F100" s="11" t="n"/>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G100" s="4" t="n"/>
       <c r="H100" s="11" t="n"/>
       <c r="I100" s="11" t="n"/>
       <c r="J100" s="9">
@@ -4561,30 +3175,16 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A101" s="11" t="n"/>
       <c r="B101" s="9">
         <f>IF(A101="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A101,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C101" s="4" t="n"/>
       <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="n"/>
       <c r="F101" s="11" t="n"/>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G101" s="4" t="n"/>
       <c r="H101" s="11" t="n"/>
       <c r="I101" s="11" t="n"/>
       <c r="J101" s="9">
@@ -4598,30 +3198,16 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A102" s="11" t="n"/>
       <c r="B102" s="9">
         <f>IF(A102="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A102,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C102" s="4" t="n"/>
       <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="n"/>
       <c r="F102" s="11" t="n"/>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G102" s="4" t="n"/>
       <c r="H102" s="11" t="n"/>
       <c r="I102" s="11" t="n"/>
       <c r="J102" s="9">
@@ -4635,30 +3221,16 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A103" s="11" t="n"/>
       <c r="B103" s="9">
         <f>IF(A103="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A103,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C103" s="4" t="n"/>
       <c r="D103" s="4" t="n"/>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="n"/>
       <c r="F103" s="11" t="n"/>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G103" s="4" t="n"/>
       <c r="H103" s="11" t="n"/>
       <c r="I103" s="11" t="n"/>
       <c r="J103" s="9">
@@ -4672,30 +3244,16 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A104" s="11" t="n"/>
       <c r="B104" s="9">
         <f>IF(A104="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A104,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C104" s="4" t="n"/>
       <c r="D104" s="4" t="n"/>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E104" s="4" t="n"/>
       <c r="F104" s="11" t="n"/>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G104" s="4" t="n"/>
       <c r="H104" s="11" t="n"/>
       <c r="I104" s="11" t="n"/>
       <c r="J104" s="9">
@@ -4709,30 +3267,16 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A105" s="11" t="n"/>
       <c r="B105" s="9">
         <f>IF(A105="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A105,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C105" s="4" t="n"/>
       <c r="D105" s="4" t="n"/>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E105" s="4" t="n"/>
       <c r="F105" s="11" t="n"/>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G105" s="4" t="n"/>
       <c r="H105" s="11" t="n"/>
       <c r="I105" s="11" t="n"/>
       <c r="J105" s="9">
@@ -4746,30 +3290,16 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A106" s="11" t="n"/>
       <c r="B106" s="9">
         <f>IF(A106="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A106,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C106" s="4" t="n"/>
       <c r="D106" s="4" t="n"/>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E106" s="4" t="n"/>
       <c r="F106" s="11" t="n"/>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G106" s="4" t="n"/>
       <c r="H106" s="11" t="n"/>
       <c r="I106" s="11" t="n"/>
       <c r="J106" s="9">
@@ -4783,30 +3313,16 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A107" s="11" t="n"/>
       <c r="B107" s="9">
         <f>IF(A107="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A107,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C107" s="4" t="n"/>
       <c r="D107" s="4" t="n"/>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E107" s="4" t="n"/>
       <c r="F107" s="11" t="n"/>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G107" s="4" t="n"/>
       <c r="H107" s="11" t="n"/>
       <c r="I107" s="11" t="n"/>
       <c r="J107" s="9">
@@ -4820,30 +3336,16 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A108" s="11" t="n"/>
       <c r="B108" s="9">
         <f>IF(A108="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A108,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C108" s="4" t="n"/>
       <c r="D108" s="4" t="n"/>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E108" s="4" t="n"/>
       <c r="F108" s="11" t="n"/>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G108" s="4" t="n"/>
       <c r="H108" s="11" t="n"/>
       <c r="I108" s="11" t="n"/>
       <c r="J108" s="9">
@@ -4857,30 +3359,16 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="A109" s="11" t="n"/>
       <c r="B109" s="9">
         <f>IF(A109="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A109,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>3A D2</t>
-        </is>
-      </c>
+      <c r="C109" s="4" t="n"/>
       <c r="D109" s="4" t="n"/>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="n"/>
       <c r="F109" s="11" t="n"/>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G109" s="4" t="n"/>
       <c r="H109" s="11" t="n"/>
       <c r="I109" s="11" t="n"/>
       <c r="J109" s="9">
@@ -4894,30 +3382,16 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A110" s="11" t="n"/>
       <c r="B110" s="9">
         <f>IF(A110="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A110,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C110" s="4" t="n"/>
       <c r="D110" s="4" t="n"/>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="n"/>
       <c r="F110" s="11" t="n"/>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G110" s="4" t="n"/>
       <c r="H110" s="11" t="n"/>
       <c r="I110" s="11" t="n"/>
       <c r="J110" s="9">
@@ -4931,30 +3405,16 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A111" s="11" t="n"/>
       <c r="B111" s="9">
         <f>IF(A111="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A111,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C111" s="4" t="n"/>
       <c r="D111" s="4" t="n"/>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="n"/>
       <c r="F111" s="11" t="n"/>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G111" s="4" t="n"/>
       <c r="H111" s="11" t="n"/>
       <c r="I111" s="11" t="n"/>
       <c r="J111" s="9">
@@ -4968,30 +3428,16 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A112" s="11" t="n"/>
       <c r="B112" s="9">
         <f>IF(A112="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A112,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C112" s="4" t="n"/>
       <c r="D112" s="4" t="n"/>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="n"/>
       <c r="F112" s="11" t="n"/>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G112" s="4" t="n"/>
       <c r="H112" s="11" t="n"/>
       <c r="I112" s="11" t="n"/>
       <c r="J112" s="9">
@@ -5005,30 +3451,16 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A113" s="11" t="n"/>
       <c r="B113" s="9">
         <f>IF(A113="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A113,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C113" s="4" t="n"/>
       <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="n"/>
       <c r="F113" s="11" t="n"/>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G113" s="4" t="n"/>
       <c r="H113" s="11" t="n"/>
       <c r="I113" s="11" t="n"/>
       <c r="J113" s="9">
@@ -5042,30 +3474,16 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A114" s="11" t="n"/>
       <c r="B114" s="9">
         <f>IF(A114="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A114,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C114" s="4" t="n"/>
       <c r="D114" s="4" t="n"/>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="n"/>
       <c r="F114" s="11" t="n"/>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G114" s="4" t="n"/>
       <c r="H114" s="11" t="n"/>
       <c r="I114" s="11" t="n"/>
       <c r="J114" s="9">
@@ -5079,30 +3497,16 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A115" s="11" t="n"/>
       <c r="B115" s="9">
         <f>IF(A115="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A115,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C115" s="4" t="n"/>
       <c r="D115" s="4" t="n"/>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="n"/>
       <c r="F115" s="11" t="n"/>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G115" s="4" t="n"/>
       <c r="H115" s="11" t="n"/>
       <c r="I115" s="11" t="n"/>
       <c r="J115" s="9">
@@ -5116,30 +3520,16 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A116" s="11" t="n"/>
       <c r="B116" s="9">
         <f>IF(A116="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A116,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C116" s="4" t="n"/>
       <c r="D116" s="4" t="n"/>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="n"/>
       <c r="F116" s="11" t="n"/>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G116" s="4" t="n"/>
       <c r="H116" s="11" t="n"/>
       <c r="I116" s="11" t="n"/>
       <c r="J116" s="9">
@@ -5153,30 +3543,16 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A117" s="11" t="n"/>
       <c r="B117" s="9">
         <f>IF(A117="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A117,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C117" s="4" t="n"/>
       <c r="D117" s="4" t="n"/>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="n"/>
       <c r="F117" s="11" t="n"/>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G117" s="4" t="n"/>
       <c r="H117" s="11" t="n"/>
       <c r="I117" s="11" t="n"/>
       <c r="J117" s="9">
@@ -5190,30 +3566,16 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A118" s="11" t="n"/>
       <c r="B118" s="9">
         <f>IF(A118="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A118,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C118" s="4" t="n"/>
       <c r="D118" s="4" t="n"/>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="n"/>
       <c r="F118" s="11" t="n"/>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G118" s="4" t="n"/>
       <c r="H118" s="11" t="n"/>
       <c r="I118" s="11" t="n"/>
       <c r="J118" s="9">
@@ -5227,30 +3589,16 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A119" s="11" t="n"/>
       <c r="B119" s="9">
         <f>IF(A119="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A119,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C119" s="4" t="n"/>
       <c r="D119" s="4" t="n"/>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="n"/>
       <c r="F119" s="11" t="n"/>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G119" s="4" t="n"/>
       <c r="H119" s="11" t="n"/>
       <c r="I119" s="11" t="n"/>
       <c r="J119" s="9">
@@ -5264,30 +3612,16 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A120" s="11" t="n"/>
       <c r="B120" s="9">
         <f>IF(A120="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A120,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C120" s="4" t="n"/>
       <c r="D120" s="4" t="n"/>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="n"/>
       <c r="F120" s="11" t="n"/>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G120" s="4" t="n"/>
       <c r="H120" s="11" t="n"/>
       <c r="I120" s="11" t="n"/>
       <c r="J120" s="9">
@@ -5301,30 +3635,16 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A121" s="11" t="n"/>
       <c r="B121" s="9">
         <f>IF(A121="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A121,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C121" s="4" t="n"/>
       <c r="D121" s="4" t="n"/>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="n"/>
       <c r="F121" s="11" t="n"/>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G121" s="4" t="n"/>
       <c r="H121" s="11" t="n"/>
       <c r="I121" s="11" t="n"/>
       <c r="J121" s="9">
@@ -5338,30 +3658,16 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A122" s="11" t="n"/>
       <c r="B122" s="9">
         <f>IF(A122="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A122,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C122" s="4" t="n"/>
       <c r="D122" s="4" t="n"/>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="n"/>
       <c r="F122" s="11" t="n"/>
-      <c r="G122" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G122" s="4" t="n"/>
       <c r="H122" s="11" t="n"/>
       <c r="I122" s="11" t="n"/>
       <c r="J122" s="9">
@@ -5375,30 +3681,16 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A123" s="11" t="n"/>
       <c r="B123" s="9">
         <f>IF(A123="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A123,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C123" s="4" t="n"/>
       <c r="D123" s="4" t="n"/>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="n"/>
       <c r="F123" s="11" t="n"/>
-      <c r="G123" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G123" s="4" t="n"/>
       <c r="H123" s="11" t="n"/>
       <c r="I123" s="11" t="n"/>
       <c r="J123" s="9">
@@ -5412,30 +3704,16 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A124" s="11" t="n"/>
       <c r="B124" s="9">
         <f>IF(A124="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A124,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C124" s="4" t="n"/>
       <c r="D124" s="4" t="n"/>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="n"/>
       <c r="F124" s="11" t="n"/>
-      <c r="G124" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G124" s="4" t="n"/>
       <c r="H124" s="11" t="n"/>
       <c r="I124" s="11" t="n"/>
       <c r="J124" s="9">
@@ -5449,30 +3727,16 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A125" s="11" t="n"/>
       <c r="B125" s="9">
         <f>IF(A125="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A125,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C125" s="4" t="n"/>
       <c r="D125" s="4" t="n"/>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="n"/>
       <c r="F125" s="11" t="n"/>
-      <c r="G125" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G125" s="4" t="n"/>
       <c r="H125" s="11" t="n"/>
       <c r="I125" s="11" t="n"/>
       <c r="J125" s="9">
@@ -5486,30 +3750,16 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A126" s="11" t="n"/>
       <c r="B126" s="9">
         <f>IF(A126="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A126,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C126" s="4" t="n"/>
       <c r="D126" s="4" t="n"/>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="n"/>
       <c r="F126" s="11" t="n"/>
-      <c r="G126" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G126" s="4" t="n"/>
       <c r="H126" s="11" t="n"/>
       <c r="I126" s="11" t="n"/>
       <c r="J126" s="9">
@@ -5523,30 +3773,16 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A127" s="11" t="n"/>
       <c r="B127" s="9">
         <f>IF(A127="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A127,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C127" s="4" t="n"/>
       <c r="D127" s="4" t="n"/>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="n"/>
       <c r="F127" s="11" t="n"/>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G127" s="4" t="n"/>
       <c r="H127" s="11" t="n"/>
       <c r="I127" s="11" t="n"/>
       <c r="J127" s="9">
@@ -5560,30 +3796,16 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A128" s="11" t="n"/>
       <c r="B128" s="9">
         <f>IF(A128="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A128,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C128" s="4" t="n"/>
       <c r="D128" s="4" t="n"/>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="n"/>
       <c r="F128" s="11" t="n"/>
-      <c r="G128" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G128" s="4" t="n"/>
       <c r="H128" s="11" t="n"/>
       <c r="I128" s="11" t="n"/>
       <c r="J128" s="9">
@@ -5597,30 +3819,16 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A129" s="11" t="n"/>
       <c r="B129" s="9">
         <f>IF(A129="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A129,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C129" s="4" t="n"/>
       <c r="D129" s="4" t="n"/>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="n"/>
       <c r="F129" s="11" t="n"/>
-      <c r="G129" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G129" s="4" t="n"/>
       <c r="H129" s="11" t="n"/>
       <c r="I129" s="11" t="n"/>
       <c r="J129" s="9">
@@ -5634,30 +3842,16 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="A130" s="11" t="n"/>
       <c r="B130" s="9">
         <f>IF(A130="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A130,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>4A D1</t>
-        </is>
-      </c>
+      <c r="C130" s="4" t="n"/>
       <c r="D130" s="4" t="n"/>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="n"/>
       <c r="F130" s="11" t="n"/>
-      <c r="G130" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G130" s="4" t="n"/>
       <c r="H130" s="11" t="n"/>
       <c r="I130" s="11" t="n"/>
       <c r="J130" s="9">
@@ -5671,30 +3865,16 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A131" s="11" t="n"/>
       <c r="B131" s="9">
         <f>IF(A131="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A131,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C131" s="4" t="n"/>
       <c r="D131" s="4" t="n"/>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="n"/>
       <c r="F131" s="11" t="n"/>
-      <c r="G131" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G131" s="4" t="n"/>
       <c r="H131" s="11" t="n"/>
       <c r="I131" s="11" t="n"/>
       <c r="J131" s="9">
@@ -5708,30 +3888,16 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A132" s="11" t="n"/>
       <c r="B132" s="9">
         <f>IF(A132="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A132,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C132" s="4" t="n"/>
       <c r="D132" s="4" t="n"/>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="n"/>
       <c r="F132" s="11" t="n"/>
-      <c r="G132" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G132" s="4" t="n"/>
       <c r="H132" s="11" t="n"/>
       <c r="I132" s="11" t="n"/>
       <c r="J132" s="9">
@@ -5745,30 +3911,16 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A133" s="11" t="n"/>
       <c r="B133" s="9">
         <f>IF(A133="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A133,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C133" s="4" t="n"/>
       <c r="D133" s="4" t="n"/>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="n"/>
       <c r="F133" s="11" t="n"/>
-      <c r="G133" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G133" s="4" t="n"/>
       <c r="H133" s="11" t="n"/>
       <c r="I133" s="11" t="n"/>
       <c r="J133" s="9">
@@ -5782,30 +3934,16 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A134" s="11" t="n"/>
       <c r="B134" s="9">
         <f>IF(A134="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A134,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C134" s="4" t="n"/>
       <c r="D134" s="4" t="n"/>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="n"/>
       <c r="F134" s="11" t="n"/>
-      <c r="G134" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G134" s="4" t="n"/>
       <c r="H134" s="11" t="n"/>
       <c r="I134" s="11" t="n"/>
       <c r="J134" s="9">
@@ -5819,30 +3957,16 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A135" s="11" t="n"/>
       <c r="B135" s="9">
         <f>IF(A135="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A135,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C135" s="4" t="n"/>
       <c r="D135" s="4" t="n"/>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="n"/>
       <c r="F135" s="11" t="n"/>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G135" s="4" t="n"/>
       <c r="H135" s="11" t="n"/>
       <c r="I135" s="11" t="n"/>
       <c r="J135" s="9">
@@ -5856,30 +3980,16 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A136" s="11" t="n"/>
       <c r="B136" s="9">
         <f>IF(A136="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A136,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C136" s="4" t="n"/>
       <c r="D136" s="4" t="n"/>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="n"/>
       <c r="F136" s="11" t="n"/>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G136" s="4" t="n"/>
       <c r="H136" s="11" t="n"/>
       <c r="I136" s="11" t="n"/>
       <c r="J136" s="9">
@@ -5893,30 +4003,16 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A137" s="11" t="n"/>
       <c r="B137" s="9">
         <f>IF(A137="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A137,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="n"/>
       <c r="F137" s="11" t="n"/>
-      <c r="G137" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G137" s="4" t="n"/>
       <c r="H137" s="11" t="n"/>
       <c r="I137" s="11" t="n"/>
       <c r="J137" s="9">
@@ -5930,30 +4026,16 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A138" s="11" t="n"/>
       <c r="B138" s="9">
         <f>IF(A138="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A138,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C138" s="4" t="n"/>
       <c r="D138" s="4" t="n"/>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="n"/>
       <c r="F138" s="11" t="n"/>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G138" s="4" t="n"/>
       <c r="H138" s="11" t="n"/>
       <c r="I138" s="11" t="n"/>
       <c r="J138" s="9">
@@ -5967,30 +4049,16 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A139" s="11" t="n"/>
       <c r="B139" s="9">
         <f>IF(A139="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A139,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C139" s="4" t="n"/>
       <c r="D139" s="4" t="n"/>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="n"/>
       <c r="F139" s="11" t="n"/>
-      <c r="G139" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G139" s="4" t="n"/>
       <c r="H139" s="11" t="n"/>
       <c r="I139" s="11" t="n"/>
       <c r="J139" s="9">
@@ -6004,30 +4072,16 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A140" s="11" t="n"/>
       <c r="B140" s="9">
         <f>IF(A140="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A140,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C140" s="4" t="n"/>
       <c r="D140" s="4" t="n"/>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="n"/>
       <c r="F140" s="11" t="n"/>
-      <c r="G140" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G140" s="4" t="n"/>
       <c r="H140" s="11" t="n"/>
       <c r="I140" s="11" t="n"/>
       <c r="J140" s="9">
@@ -6041,30 +4095,16 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A141" s="11" t="n"/>
       <c r="B141" s="9">
         <f>IF(A141="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A141,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C141" s="4" t="n"/>
       <c r="D141" s="4" t="n"/>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="n"/>
       <c r="F141" s="11" t="n"/>
-      <c r="G141" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G141" s="4" t="n"/>
       <c r="H141" s="11" t="n"/>
       <c r="I141" s="11" t="n"/>
       <c r="J141" s="9">
@@ -6078,30 +4118,16 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A142" s="11" t="n"/>
       <c r="B142" s="9">
         <f>IF(A142="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A142,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C142" s="4" t="n"/>
       <c r="D142" s="4" t="n"/>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="n"/>
       <c r="F142" s="11" t="n"/>
-      <c r="G142" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G142" s="4" t="n"/>
       <c r="H142" s="11" t="n"/>
       <c r="I142" s="11" t="n"/>
       <c r="J142" s="9">
@@ -6115,30 +4141,16 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A143" s="11" t="n"/>
       <c r="B143" s="9">
         <f>IF(A143="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A143,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C143" s="4" t="n"/>
       <c r="D143" s="4" t="n"/>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="n"/>
       <c r="F143" s="11" t="n"/>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G143" s="4" t="n"/>
       <c r="H143" s="11" t="n"/>
       <c r="I143" s="11" t="n"/>
       <c r="J143" s="9">
@@ -6152,30 +4164,16 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A144" s="11" t="n"/>
       <c r="B144" s="9">
         <f>IF(A144="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A144,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C144" s="4" t="n"/>
       <c r="D144" s="4" t="n"/>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="n"/>
       <c r="F144" s="11" t="n"/>
-      <c r="G144" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G144" s="4" t="n"/>
       <c r="H144" s="11" t="n"/>
       <c r="I144" s="11" t="n"/>
       <c r="J144" s="9">
@@ -6189,30 +4187,16 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A145" s="11" t="n"/>
       <c r="B145" s="9">
         <f>IF(A145="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A145,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C145" s="4" t="n"/>
       <c r="D145" s="4" t="n"/>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="n"/>
       <c r="F145" s="11" t="n"/>
-      <c r="G145" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G145" s="4" t="n"/>
       <c r="H145" s="11" t="n"/>
       <c r="I145" s="11" t="n"/>
       <c r="J145" s="9">
@@ -6226,30 +4210,16 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A146" s="11" t="n"/>
       <c r="B146" s="9">
         <f>IF(A146="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A146,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C146" s="4" t="n"/>
       <c r="D146" s="4" t="n"/>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="n"/>
       <c r="F146" s="11" t="n"/>
-      <c r="G146" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G146" s="4" t="n"/>
       <c r="H146" s="11" t="n"/>
       <c r="I146" s="11" t="n"/>
       <c r="J146" s="9">
@@ -6263,30 +4233,16 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A147" s="11" t="n"/>
       <c r="B147" s="9">
         <f>IF(A147="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A147,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C147" s="4" t="n"/>
       <c r="D147" s="4" t="n"/>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="n"/>
       <c r="F147" s="11" t="n"/>
-      <c r="G147" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G147" s="4" t="n"/>
       <c r="H147" s="11" t="n"/>
       <c r="I147" s="11" t="n"/>
       <c r="J147" s="9">
@@ -6300,30 +4256,16 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A148" s="11" t="n"/>
       <c r="B148" s="9">
         <f>IF(A148="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A148,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C148" s="4" t="n"/>
       <c r="D148" s="4" t="n"/>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="n"/>
       <c r="F148" s="11" t="n"/>
-      <c r="G148" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G148" s="4" t="n"/>
       <c r="H148" s="11" t="n"/>
       <c r="I148" s="11" t="n"/>
       <c r="J148" s="9">
@@ -6337,30 +4279,16 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A149" s="11" t="n"/>
       <c r="B149" s="9">
         <f>IF(A149="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A149,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C149" s="4" t="n"/>
       <c r="D149" s="4" t="n"/>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="n"/>
       <c r="F149" s="11" t="n"/>
-      <c r="G149" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G149" s="4" t="n"/>
       <c r="H149" s="11" t="n"/>
       <c r="I149" s="11" t="n"/>
       <c r="J149" s="9">
@@ -6374,30 +4302,16 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A150" s="11" t="n"/>
       <c r="B150" s="9">
         <f>IF(A150="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A150,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C150" s="4" t="n"/>
       <c r="D150" s="4" t="n"/>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="n"/>
       <c r="F150" s="11" t="n"/>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G150" s="4" t="n"/>
       <c r="H150" s="11" t="n"/>
       <c r="I150" s="11" t="n"/>
       <c r="J150" s="9">
@@ -6411,30 +4325,16 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="A151" s="11" t="n"/>
       <c r="B151" s="9">
         <f>IF(A151="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A151,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>4A D2</t>
-        </is>
-      </c>
+      <c r="C151" s="4" t="n"/>
       <c r="D151" s="4" t="n"/>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="n"/>
       <c r="F151" s="11" t="n"/>
-      <c r="G151" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G151" s="4" t="n"/>
       <c r="H151" s="11" t="n"/>
       <c r="I151" s="11" t="n"/>
       <c r="J151" s="9">
@@ -6448,30 +4348,16 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A152" s="11" t="n"/>
       <c r="B152" s="9">
         <f>IF(A152="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A152,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C152" s="4" t="n"/>
       <c r="D152" s="4" t="n"/>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="n"/>
       <c r="F152" s="11" t="n"/>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G152" s="4" t="n"/>
       <c r="H152" s="11" t="n"/>
       <c r="I152" s="11" t="n"/>
       <c r="J152" s="9">
@@ -6485,30 +4371,16 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A153" s="11" t="n"/>
       <c r="B153" s="9">
         <f>IF(A153="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A153,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C153" s="4" t="n"/>
       <c r="D153" s="4" t="n"/>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="n"/>
       <c r="F153" s="11" t="n"/>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G153" s="4" t="n"/>
       <c r="H153" s="11" t="n"/>
       <c r="I153" s="11" t="n"/>
       <c r="J153" s="9">
@@ -6522,30 +4394,16 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A154" s="11" t="n"/>
       <c r="B154" s="9">
         <f>IF(A154="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A154,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C154" s="4" t="n"/>
       <c r="D154" s="4" t="n"/>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="n"/>
       <c r="F154" s="11" t="n"/>
-      <c r="G154" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G154" s="4" t="n"/>
       <c r="H154" s="11" t="n"/>
       <c r="I154" s="11" t="n"/>
       <c r="J154" s="9">
@@ -6559,30 +4417,16 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A155" s="11" t="n"/>
       <c r="B155" s="9">
         <f>IF(A155="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A155,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C155" s="4" t="n"/>
       <c r="D155" s="4" t="n"/>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="n"/>
       <c r="F155" s="11" t="n"/>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G155" s="4" t="n"/>
       <c r="H155" s="11" t="n"/>
       <c r="I155" s="11" t="n"/>
       <c r="J155" s="9">
@@ -6596,30 +4440,16 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A156" s="11" t="n"/>
       <c r="B156" s="9">
         <f>IF(A156="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A156,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C156" s="4" t="n"/>
       <c r="D156" s="4" t="n"/>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="n"/>
       <c r="F156" s="11" t="n"/>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G156" s="4" t="n"/>
       <c r="H156" s="11" t="n"/>
       <c r="I156" s="11" t="n"/>
       <c r="J156" s="9">
@@ -6633,30 +4463,16 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A157" s="11" t="n"/>
       <c r="B157" s="9">
         <f>IF(A157="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A157,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C157" s="4" t="n"/>
       <c r="D157" s="4" t="n"/>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="n"/>
       <c r="F157" s="11" t="n"/>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G157" s="4" t="n"/>
       <c r="H157" s="11" t="n"/>
       <c r="I157" s="11" t="n"/>
       <c r="J157" s="9">
@@ -6670,30 +4486,16 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A158" s="11" t="n"/>
       <c r="B158" s="9">
         <f>IF(A158="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A158,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C158" s="4" t="n"/>
       <c r="D158" s="4" t="n"/>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="n"/>
       <c r="F158" s="11" t="n"/>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G158" s="4" t="n"/>
       <c r="H158" s="11" t="n"/>
       <c r="I158" s="11" t="n"/>
       <c r="J158" s="9">
@@ -6707,30 +4509,16 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A159" s="11" t="n"/>
       <c r="B159" s="9">
         <f>IF(A159="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A159,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C159" s="4" t="n"/>
       <c r="D159" s="4" t="n"/>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E159" s="4" t="n"/>
       <c r="F159" s="11" t="n"/>
-      <c r="G159" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G159" s="4" t="n"/>
       <c r="H159" s="11" t="n"/>
       <c r="I159" s="11" t="n"/>
       <c r="J159" s="9">
@@ -6744,30 +4532,16 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A160" s="11" t="n"/>
       <c r="B160" s="9">
         <f>IF(A160="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A160,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C160" s="4" t="n"/>
       <c r="D160" s="4" t="n"/>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E160" s="4" t="n"/>
       <c r="F160" s="11" t="n"/>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G160" s="4" t="n"/>
       <c r="H160" s="11" t="n"/>
       <c r="I160" s="11" t="n"/>
       <c r="J160" s="9">
@@ -6781,30 +4555,16 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A161" s="11" t="n"/>
       <c r="B161" s="9">
         <f>IF(A161="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A161,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C161" s="4" t="n"/>
       <c r="D161" s="4" t="n"/>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E161" s="4" t="n"/>
       <c r="F161" s="11" t="n"/>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G161" s="4" t="n"/>
       <c r="H161" s="11" t="n"/>
       <c r="I161" s="11" t="n"/>
       <c r="J161" s="9">
@@ -6818,30 +4578,16 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A162" s="11" t="n"/>
       <c r="B162" s="9">
         <f>IF(A162="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A162,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C162" s="4" t="n"/>
       <c r="D162" s="4" t="n"/>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E162" s="4" t="n"/>
       <c r="F162" s="11" t="n"/>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G162" s="4" t="n"/>
       <c r="H162" s="11" t="n"/>
       <c r="I162" s="11" t="n"/>
       <c r="J162" s="9">
@@ -6855,30 +4601,16 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A163" s="11" t="n"/>
       <c r="B163" s="9">
         <f>IF(A163="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A163,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C163" s="4" t="n"/>
       <c r="D163" s="4" t="n"/>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E163" s="4" t="n"/>
       <c r="F163" s="11" t="n"/>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G163" s="4" t="n"/>
       <c r="H163" s="11" t="n"/>
       <c r="I163" s="11" t="n"/>
       <c r="J163" s="9">
@@ -6892,30 +4624,16 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A164" s="11" t="n"/>
       <c r="B164" s="9">
         <f>IF(A164="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A164,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C164" s="4" t="n"/>
       <c r="D164" s="4" t="n"/>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E164" s="4" t="n"/>
       <c r="F164" s="11" t="n"/>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G164" s="4" t="n"/>
       <c r="H164" s="11" t="n"/>
       <c r="I164" s="11" t="n"/>
       <c r="J164" s="9">
@@ -6929,30 +4647,16 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A165" s="11" t="n"/>
       <c r="B165" s="9">
         <f>IF(A165="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A165,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C165" s="4" t="n"/>
       <c r="D165" s="4" t="n"/>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E165" s="4" t="n"/>
       <c r="F165" s="11" t="n"/>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G165" s="4" t="n"/>
       <c r="H165" s="11" t="n"/>
       <c r="I165" s="11" t="n"/>
       <c r="J165" s="9">
@@ -6966,30 +4670,16 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A166" s="11" t="n"/>
       <c r="B166" s="9">
         <f>IF(A166="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A166,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C166" s="4" t="n"/>
       <c r="D166" s="4" t="n"/>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E166" s="4" t="n"/>
       <c r="F166" s="11" t="n"/>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G166" s="4" t="n"/>
       <c r="H166" s="11" t="n"/>
       <c r="I166" s="11" t="n"/>
       <c r="J166" s="9">
@@ -7003,30 +4693,16 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A167" s="11" t="n"/>
       <c r="B167" s="9">
         <f>IF(A167="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A167,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C167" s="4" t="n"/>
       <c r="D167" s="4" t="n"/>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E167" s="4" t="n"/>
       <c r="F167" s="11" t="n"/>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G167" s="4" t="n"/>
       <c r="H167" s="11" t="n"/>
       <c r="I167" s="11" t="n"/>
       <c r="J167" s="9">
@@ -7040,30 +4716,16 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A168" s="11" t="n"/>
       <c r="B168" s="9">
         <f>IF(A168="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A168,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C168" s="4" t="n"/>
       <c r="D168" s="4" t="n"/>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E168" s="4" t="n"/>
       <c r="F168" s="11" t="n"/>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G168" s="4" t="n"/>
       <c r="H168" s="11" t="n"/>
       <c r="I168" s="11" t="n"/>
       <c r="J168" s="9">
@@ -7077,30 +4739,16 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A169" s="11" t="n"/>
       <c r="B169" s="9">
         <f>IF(A169="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A169,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C169" s="4" t="n"/>
       <c r="D169" s="4" t="n"/>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E169" s="4" t="n"/>
       <c r="F169" s="11" t="n"/>
-      <c r="G169" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G169" s="4" t="n"/>
       <c r="H169" s="11" t="n"/>
       <c r="I169" s="11" t="n"/>
       <c r="J169" s="9">
@@ -7114,30 +4762,16 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A170" s="11" t="n"/>
       <c r="B170" s="9">
         <f>IF(A170="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A170,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C170" s="4" t="n"/>
       <c r="D170" s="4" t="n"/>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E170" s="4" t="n"/>
       <c r="F170" s="11" t="n"/>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G170" s="4" t="n"/>
       <c r="H170" s="11" t="n"/>
       <c r="I170" s="11" t="n"/>
       <c r="J170" s="9">
@@ -7151,30 +4785,16 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A171" s="11" t="n"/>
       <c r="B171" s="9">
         <f>IF(A171="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A171,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C171" s="4" t="n"/>
       <c r="D171" s="4" t="n"/>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E171" s="4" t="n"/>
       <c r="F171" s="11" t="n"/>
-      <c r="G171" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G171" s="4" t="n"/>
       <c r="H171" s="11" t="n"/>
       <c r="I171" s="11" t="n"/>
       <c r="J171" s="9">
@@ -7188,30 +4808,16 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="A172" s="11" t="n"/>
       <c r="B172" s="9">
         <f>IF(A172="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A172,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>5A D1</t>
-        </is>
-      </c>
+      <c r="C172" s="4" t="n"/>
       <c r="D172" s="4" t="n"/>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E172" s="4" t="n"/>
       <c r="F172" s="11" t="n"/>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G172" s="4" t="n"/>
       <c r="H172" s="11" t="n"/>
       <c r="I172" s="11" t="n"/>
       <c r="J172" s="9">
@@ -7225,30 +4831,16 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A173" s="11" t="n"/>
       <c r="B173" s="9">
         <f>IF(A173="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A173,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C173" s="4" t="n"/>
       <c r="D173" s="4" t="n"/>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E173" s="4" t="n"/>
       <c r="F173" s="11" t="n"/>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G173" s="4" t="n"/>
       <c r="H173" s="11" t="n"/>
       <c r="I173" s="11" t="n"/>
       <c r="J173" s="9">
@@ -7262,30 +4854,16 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A174" s="11" t="n"/>
       <c r="B174" s="9">
         <f>IF(A174="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A174,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C174" s="4" t="n"/>
       <c r="D174" s="4" t="n"/>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E174" s="4" t="n"/>
       <c r="F174" s="11" t="n"/>
-      <c r="G174" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G174" s="4" t="n"/>
       <c r="H174" s="11" t="n"/>
       <c r="I174" s="11" t="n"/>
       <c r="J174" s="9">
@@ -7299,30 +4877,16 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A175" s="11" t="n"/>
       <c r="B175" s="9">
         <f>IF(A175="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A175,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C175" s="4" t="n"/>
       <c r="D175" s="4" t="n"/>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E175" s="4" t="n"/>
       <c r="F175" s="11" t="n"/>
-      <c r="G175" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G175" s="4" t="n"/>
       <c r="H175" s="11" t="n"/>
       <c r="I175" s="11" t="n"/>
       <c r="J175" s="9">
@@ -7336,30 +4900,16 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A176" s="11" t="n"/>
       <c r="B176" s="9">
         <f>IF(A176="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A176,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C176" s="4" t="n"/>
       <c r="D176" s="4" t="n"/>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E176" s="4" t="n"/>
       <c r="F176" s="11" t="n"/>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G176" s="4" t="n"/>
       <c r="H176" s="11" t="n"/>
       <c r="I176" s="11" t="n"/>
       <c r="J176" s="9">
@@ -7373,30 +4923,16 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A177" s="11" t="n"/>
       <c r="B177" s="9">
         <f>IF(A177="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A177,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C177" s="4" t="n"/>
       <c r="D177" s="4" t="n"/>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E177" s="4" t="n"/>
       <c r="F177" s="11" t="n"/>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G177" s="4" t="n"/>
       <c r="H177" s="11" t="n"/>
       <c r="I177" s="11" t="n"/>
       <c r="J177" s="9">
@@ -7410,30 +4946,16 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A178" s="11" t="n"/>
       <c r="B178" s="9">
         <f>IF(A178="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A178,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C178" s="4" t="n"/>
       <c r="D178" s="4" t="n"/>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E178" s="4" t="n"/>
       <c r="F178" s="11" t="n"/>
-      <c r="G178" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G178" s="4" t="n"/>
       <c r="H178" s="11" t="n"/>
       <c r="I178" s="11" t="n"/>
       <c r="J178" s="9">
@@ -7447,30 +4969,16 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A179" s="11" t="n"/>
       <c r="B179" s="9">
         <f>IF(A179="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A179,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C179" s="4" t="n"/>
       <c r="D179" s="4" t="n"/>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E179" s="4" t="n"/>
       <c r="F179" s="11" t="n"/>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G179" s="4" t="n"/>
       <c r="H179" s="11" t="n"/>
       <c r="I179" s="11" t="n"/>
       <c r="J179" s="9">
@@ -7484,30 +4992,16 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A180" s="11" t="n"/>
       <c r="B180" s="9">
         <f>IF(A180="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A180,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C180" s="4" t="n"/>
       <c r="D180" s="4" t="n"/>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E180" s="4" t="n"/>
       <c r="F180" s="11" t="n"/>
-      <c r="G180" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G180" s="4" t="n"/>
       <c r="H180" s="11" t="n"/>
       <c r="I180" s="11" t="n"/>
       <c r="J180" s="9">
@@ -7521,30 +5015,16 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A181" s="11" t="n"/>
       <c r="B181" s="9">
         <f>IF(A181="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A181,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C181" s="4" t="n"/>
       <c r="D181" s="4" t="n"/>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E181" s="4" t="n"/>
       <c r="F181" s="11" t="n"/>
-      <c r="G181" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G181" s="4" t="n"/>
       <c r="H181" s="11" t="n"/>
       <c r="I181" s="11" t="n"/>
       <c r="J181" s="9">
@@ -7558,30 +5038,16 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A182" s="11" t="n"/>
       <c r="B182" s="9">
         <f>IF(A182="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A182,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C182" s="4" t="n"/>
       <c r="D182" s="4" t="n"/>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E182" s="4" t="n"/>
       <c r="F182" s="11" t="n"/>
-      <c r="G182" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G182" s="4" t="n"/>
       <c r="H182" s="11" t="n"/>
       <c r="I182" s="11" t="n"/>
       <c r="J182" s="9">
@@ -7595,30 +5061,16 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A183" s="11" t="n"/>
       <c r="B183" s="9">
         <f>IF(A183="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A183,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C183" s="4" t="n"/>
       <c r="D183" s="4" t="n"/>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E183" s="4" t="n"/>
       <c r="F183" s="11" t="n"/>
-      <c r="G183" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G183" s="4" t="n"/>
       <c r="H183" s="11" t="n"/>
       <c r="I183" s="11" t="n"/>
       <c r="J183" s="9">
@@ -7632,30 +5084,16 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A184" s="11" t="n"/>
       <c r="B184" s="9">
         <f>IF(A184="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A184,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C184" s="4" t="n"/>
       <c r="D184" s="4" t="n"/>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E184" s="4" t="n"/>
       <c r="F184" s="11" t="n"/>
-      <c r="G184" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G184" s="4" t="n"/>
       <c r="H184" s="11" t="n"/>
       <c r="I184" s="11" t="n"/>
       <c r="J184" s="9">
@@ -7669,30 +5107,16 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A185" s="11" t="n"/>
       <c r="B185" s="9">
         <f>IF(A185="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A185,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C185" s="4" t="n"/>
       <c r="D185" s="4" t="n"/>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E185" s="4" t="n"/>
       <c r="F185" s="11" t="n"/>
-      <c r="G185" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G185" s="4" t="n"/>
       <c r="H185" s="11" t="n"/>
       <c r="I185" s="11" t="n"/>
       <c r="J185" s="9">
@@ -7706,30 +5130,16 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A186" s="11" t="n"/>
       <c r="B186" s="9">
         <f>IF(A186="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A186,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C186" s="4" t="n"/>
       <c r="D186" s="4" t="n"/>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E186" s="4" t="n"/>
       <c r="F186" s="11" t="n"/>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G186" s="4" t="n"/>
       <c r="H186" s="11" t="n"/>
       <c r="I186" s="11" t="n"/>
       <c r="J186" s="9">
@@ -7743,30 +5153,16 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A187" s="11" t="n"/>
       <c r="B187" s="9">
         <f>IF(A187="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A187,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C187" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C187" s="4" t="n"/>
       <c r="D187" s="4" t="n"/>
-      <c r="E187" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E187" s="4" t="n"/>
       <c r="F187" s="11" t="n"/>
-      <c r="G187" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G187" s="4" t="n"/>
       <c r="H187" s="11" t="n"/>
       <c r="I187" s="11" t="n"/>
       <c r="J187" s="9">
@@ -7780,30 +5176,16 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A188" s="11" t="n"/>
       <c r="B188" s="9">
         <f>IF(A188="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A188,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C188" s="4" t="n"/>
       <c r="D188" s="4" t="n"/>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E188" s="4" t="n"/>
       <c r="F188" s="11" t="n"/>
-      <c r="G188" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G188" s="4" t="n"/>
       <c r="H188" s="11" t="n"/>
       <c r="I188" s="11" t="n"/>
       <c r="J188" s="9">
@@ -7817,30 +5199,16 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A189" s="11" t="n"/>
       <c r="B189" s="9">
         <f>IF(A189="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A189,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C189" s="4" t="n"/>
       <c r="D189" s="4" t="n"/>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E189" s="4" t="n"/>
       <c r="F189" s="11" t="n"/>
-      <c r="G189" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G189" s="4" t="n"/>
       <c r="H189" s="11" t="n"/>
       <c r="I189" s="11" t="n"/>
       <c r="J189" s="9">
@@ -7854,30 +5222,16 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A190" s="11" t="n"/>
       <c r="B190" s="9">
         <f>IF(A190="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A190,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C190" s="4" t="n"/>
       <c r="D190" s="4" t="n"/>
-      <c r="E190" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E190" s="4" t="n"/>
       <c r="F190" s="11" t="n"/>
-      <c r="G190" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G190" s="4" t="n"/>
       <c r="H190" s="11" t="n"/>
       <c r="I190" s="11" t="n"/>
       <c r="J190" s="9">
@@ -7891,30 +5245,16 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A191" s="11" t="n"/>
       <c r="B191" s="9">
         <f>IF(A191="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A191,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C191" s="4" t="n"/>
       <c r="D191" s="4" t="n"/>
-      <c r="E191" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E191" s="4" t="n"/>
       <c r="F191" s="11" t="n"/>
-      <c r="G191" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G191" s="4" t="n"/>
       <c r="H191" s="11" t="n"/>
       <c r="I191" s="11" t="n"/>
       <c r="J191" s="9">
@@ -7928,30 +5268,16 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A192" s="11" t="n"/>
       <c r="B192" s="9">
         <f>IF(A192="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A192,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C192" s="4" t="n"/>
       <c r="D192" s="4" t="n"/>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E192" s="4" t="n"/>
       <c r="F192" s="11" t="n"/>
-      <c r="G192" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G192" s="4" t="n"/>
       <c r="H192" s="11" t="n"/>
       <c r="I192" s="11" t="n"/>
       <c r="J192" s="9">
@@ -7965,30 +5291,16 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="A193" s="11" t="n"/>
       <c r="B193" s="9">
         <f>IF(A193="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A193,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>5A D2</t>
-        </is>
-      </c>
+      <c r="C193" s="4" t="n"/>
       <c r="D193" s="4" t="n"/>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E193" s="4" t="n"/>
       <c r="F193" s="11" t="n"/>
-      <c r="G193" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G193" s="4" t="n"/>
       <c r="H193" s="11" t="n"/>
       <c r="I193" s="11" t="n"/>
       <c r="J193" s="9">
@@ -8002,30 +5314,16 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A194" s="11" t="n"/>
       <c r="B194" s="9">
         <f>IF(A194="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A194,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C194" s="4" t="n"/>
       <c r="D194" s="4" t="n"/>
-      <c r="E194" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E194" s="4" t="n"/>
       <c r="F194" s="11" t="n"/>
-      <c r="G194" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G194" s="4" t="n"/>
       <c r="H194" s="11" t="n"/>
       <c r="I194" s="11" t="n"/>
       <c r="J194" s="9">
@@ -8039,30 +5337,16 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A195" s="11" t="n"/>
       <c r="B195" s="9">
         <f>IF(A195="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A195,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C195" s="4" t="n"/>
       <c r="D195" s="4" t="n"/>
-      <c r="E195" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E195" s="4" t="n"/>
       <c r="F195" s="11" t="n"/>
-      <c r="G195" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G195" s="4" t="n"/>
       <c r="H195" s="11" t="n"/>
       <c r="I195" s="11" t="n"/>
       <c r="J195" s="9">
@@ -8076,30 +5360,16 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A196" s="11" t="n"/>
       <c r="B196" s="9">
         <f>IF(A196="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A196,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C196" s="4" t="n"/>
       <c r="D196" s="4" t="n"/>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E196" s="4" t="n"/>
       <c r="F196" s="11" t="n"/>
-      <c r="G196" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G196" s="4" t="n"/>
       <c r="H196" s="11" t="n"/>
       <c r="I196" s="11" t="n"/>
       <c r="J196" s="9">
@@ -8113,30 +5383,16 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A197" s="11" t="n"/>
       <c r="B197" s="9">
         <f>IF(A197="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A197,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C197" s="4" t="n"/>
       <c r="D197" s="4" t="n"/>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E197" s="4" t="n"/>
       <c r="F197" s="11" t="n"/>
-      <c r="G197" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G197" s="4" t="n"/>
       <c r="H197" s="11" t="n"/>
       <c r="I197" s="11" t="n"/>
       <c r="J197" s="9">
@@ -8150,30 +5406,16 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A198" s="11" t="n"/>
       <c r="B198" s="9">
         <f>IF(A198="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A198,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C198" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C198" s="4" t="n"/>
       <c r="D198" s="4" t="n"/>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E198" s="4" t="n"/>
       <c r="F198" s="11" t="n"/>
-      <c r="G198" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G198" s="4" t="n"/>
       <c r="H198" s="11" t="n"/>
       <c r="I198" s="11" t="n"/>
       <c r="J198" s="9">
@@ -8187,30 +5429,16 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A199" s="11" t="n"/>
       <c r="B199" s="9">
         <f>IF(A199="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A199,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C199" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C199" s="4" t="n"/>
       <c r="D199" s="4" t="n"/>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E199" s="4" t="n"/>
       <c r="F199" s="11" t="n"/>
-      <c r="G199" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G199" s="4" t="n"/>
       <c r="H199" s="11" t="n"/>
       <c r="I199" s="11" t="n"/>
       <c r="J199" s="9">
@@ -8224,30 +5452,16 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A200" s="11" t="n"/>
       <c r="B200" s="9">
         <f>IF(A200="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A200,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C200" s="4" t="n"/>
       <c r="D200" s="4" t="n"/>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E200" s="4" t="n"/>
       <c r="F200" s="11" t="n"/>
-      <c r="G200" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G200" s="4" t="n"/>
       <c r="H200" s="11" t="n"/>
       <c r="I200" s="11" t="n"/>
       <c r="J200" s="9">
@@ -8261,30 +5475,16 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A201" s="11" t="n"/>
       <c r="B201" s="9">
         <f>IF(A201="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A201,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C201" s="4" t="n"/>
       <c r="D201" s="4" t="n"/>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E201" s="4" t="n"/>
       <c r="F201" s="11" t="n"/>
-      <c r="G201" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G201" s="4" t="n"/>
       <c r="H201" s="11" t="n"/>
       <c r="I201" s="11" t="n"/>
       <c r="J201" s="9">
@@ -8298,30 +5498,16 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A202" s="11" t="n"/>
       <c r="B202" s="9">
         <f>IF(A202="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A202,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C202" s="4" t="n"/>
       <c r="D202" s="4" t="n"/>
-      <c r="E202" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E202" s="4" t="n"/>
       <c r="F202" s="11" t="n"/>
-      <c r="G202" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G202" s="4" t="n"/>
       <c r="H202" s="11" t="n"/>
       <c r="I202" s="11" t="n"/>
       <c r="J202" s="9">
@@ -8335,30 +5521,16 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A203" s="11" t="n"/>
       <c r="B203" s="9">
         <f>IF(A203="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A203,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C203" s="4" t="n"/>
       <c r="D203" s="4" t="n"/>
-      <c r="E203" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E203" s="4" t="n"/>
       <c r="F203" s="11" t="n"/>
-      <c r="G203" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G203" s="4" t="n"/>
       <c r="H203" s="11" t="n"/>
       <c r="I203" s="11" t="n"/>
       <c r="J203" s="9">
@@ -8372,30 +5544,16 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A204" s="11" t="n"/>
       <c r="B204" s="9">
         <f>IF(A204="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A204,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C204" s="4" t="n"/>
       <c r="D204" s="4" t="n"/>
-      <c r="E204" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E204" s="4" t="n"/>
       <c r="F204" s="11" t="n"/>
-      <c r="G204" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G204" s="4" t="n"/>
       <c r="H204" s="11" t="n"/>
       <c r="I204" s="11" t="n"/>
       <c r="J204" s="9">
@@ -8409,30 +5567,16 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A205" s="11" t="n"/>
       <c r="B205" s="9">
         <f>IF(A205="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A205,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C205" s="4" t="n"/>
       <c r="D205" s="4" t="n"/>
-      <c r="E205" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E205" s="4" t="n"/>
       <c r="F205" s="11" t="n"/>
-      <c r="G205" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G205" s="4" t="n"/>
       <c r="H205" s="11" t="n"/>
       <c r="I205" s="11" t="n"/>
       <c r="J205" s="9">
@@ -8446,30 +5590,16 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A206" s="11" t="n"/>
       <c r="B206" s="9">
         <f>IF(A206="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A206,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C206" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C206" s="4" t="n"/>
       <c r="D206" s="4" t="n"/>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E206" s="4" t="n"/>
       <c r="F206" s="11" t="n"/>
-      <c r="G206" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G206" s="4" t="n"/>
       <c r="H206" s="11" t="n"/>
       <c r="I206" s="11" t="n"/>
       <c r="J206" s="9">
@@ -8483,30 +5613,16 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A207" s="11" t="n"/>
       <c r="B207" s="9">
         <f>IF(A207="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A207,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C207" s="4" t="n"/>
       <c r="D207" s="4" t="n"/>
-      <c r="E207" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E207" s="4" t="n"/>
       <c r="F207" s="11" t="n"/>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G207" s="4" t="n"/>
       <c r="H207" s="11" t="n"/>
       <c r="I207" s="11" t="n"/>
       <c r="J207" s="9">
@@ -8520,30 +5636,16 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A208" s="11" t="n"/>
       <c r="B208" s="9">
         <f>IF(A208="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A208,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C208" s="4" t="n"/>
       <c r="D208" s="4" t="n"/>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E208" s="4" t="n"/>
       <c r="F208" s="11" t="n"/>
-      <c r="G208" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G208" s="4" t="n"/>
       <c r="H208" s="11" t="n"/>
       <c r="I208" s="11" t="n"/>
       <c r="J208" s="9">
@@ -8557,30 +5659,16 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A209" s="11" t="n"/>
       <c r="B209" s="9">
         <f>IF(A209="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A209,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C209" s="4" t="n"/>
       <c r="D209" s="4" t="n"/>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E209" s="4" t="n"/>
       <c r="F209" s="11" t="n"/>
-      <c r="G209" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G209" s="4" t="n"/>
       <c r="H209" s="11" t="n"/>
       <c r="I209" s="11" t="n"/>
       <c r="J209" s="9">
@@ -8594,30 +5682,16 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A210" s="11" t="n"/>
       <c r="B210" s="9">
         <f>IF(A210="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A210,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C210" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C210" s="4" t="n"/>
       <c r="D210" s="4" t="n"/>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E210" s="4" t="n"/>
       <c r="F210" s="11" t="n"/>
-      <c r="G210" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G210" s="4" t="n"/>
       <c r="H210" s="11" t="n"/>
       <c r="I210" s="11" t="n"/>
       <c r="J210" s="9">
@@ -8631,30 +5705,16 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A211" s="11" t="n"/>
       <c r="B211" s="9">
         <f>IF(A211="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A211,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C211" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C211" s="4" t="n"/>
       <c r="D211" s="4" t="n"/>
-      <c r="E211" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E211" s="4" t="n"/>
       <c r="F211" s="11" t="n"/>
-      <c r="G211" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G211" s="4" t="n"/>
       <c r="H211" s="11" t="n"/>
       <c r="I211" s="11" t="n"/>
       <c r="J211" s="9">
@@ -8668,30 +5728,16 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A212" s="11" t="n"/>
       <c r="B212" s="9">
         <f>IF(A212="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A212,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C212" s="4" t="n"/>
       <c r="D212" s="4" t="n"/>
-      <c r="E212" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E212" s="4" t="n"/>
       <c r="F212" s="11" t="n"/>
-      <c r="G212" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G212" s="4" t="n"/>
       <c r="H212" s="11" t="n"/>
       <c r="I212" s="11" t="n"/>
       <c r="J212" s="9">
@@ -8705,30 +5751,16 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A213" s="11" t="n"/>
       <c r="B213" s="9">
         <f>IF(A213="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A213,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C213" s="4" t="n"/>
       <c r="D213" s="4" t="n"/>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E213" s="4" t="n"/>
       <c r="F213" s="11" t="n"/>
-      <c r="G213" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G213" s="4" t="n"/>
       <c r="H213" s="11" t="n"/>
       <c r="I213" s="11" t="n"/>
       <c r="J213" s="9">
@@ -8742,30 +5774,16 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="A214" s="11" t="n"/>
       <c r="B214" s="9">
         <f>IF(A214="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A214,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>6A D1</t>
-        </is>
-      </c>
+      <c r="C214" s="4" t="n"/>
       <c r="D214" s="4" t="n"/>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E214" s="4" t="n"/>
       <c r="F214" s="11" t="n"/>
-      <c r="G214" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G214" s="4" t="n"/>
       <c r="H214" s="11" t="n"/>
       <c r="I214" s="11" t="n"/>
       <c r="J214" s="9">
@@ -8779,30 +5797,16 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A215" s="11" t="n"/>
       <c r="B215" s="9">
         <f>IF(A215="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A215,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C215" s="4" t="n"/>
       <c r="D215" s="4" t="n"/>
-      <c r="E215" s="4" t="inlineStr">
-        <is>
-          <t>Winner G1</t>
-        </is>
-      </c>
+      <c r="E215" s="4" t="n"/>
       <c r="F215" s="11" t="n"/>
-      <c r="G215" s="4" t="inlineStr">
-        <is>
-          <t>Winner G2</t>
-        </is>
-      </c>
+      <c r="G215" s="4" t="n"/>
       <c r="H215" s="11" t="n"/>
       <c r="I215" s="11" t="n"/>
       <c r="J215" s="9">
@@ -8816,30 +5820,16 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A216" s="11" t="n"/>
       <c r="B216" s="9">
         <f>IF(A216="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A216,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C216" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C216" s="4" t="n"/>
       <c r="D216" s="4" t="n"/>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>Winner G3</t>
-        </is>
-      </c>
+      <c r="E216" s="4" t="n"/>
       <c r="F216" s="11" t="n"/>
-      <c r="G216" s="4" t="inlineStr">
-        <is>
-          <t>Winner G4</t>
-        </is>
-      </c>
+      <c r="G216" s="4" t="n"/>
       <c r="H216" s="11" t="n"/>
       <c r="I216" s="11" t="n"/>
       <c r="J216" s="9">
@@ -8853,30 +5843,16 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A217" s="11" t="n"/>
       <c r="B217" s="9">
         <f>IF(A217="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A217,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C217" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C217" s="4" t="n"/>
       <c r="D217" s="4" t="n"/>
-      <c r="E217" s="4" t="inlineStr">
-        <is>
-          <t>Winner G5</t>
-        </is>
-      </c>
+      <c r="E217" s="4" t="n"/>
       <c r="F217" s="11" t="n"/>
-      <c r="G217" s="4" t="inlineStr">
-        <is>
-          <t>Winner G6</t>
-        </is>
-      </c>
+      <c r="G217" s="4" t="n"/>
       <c r="H217" s="11" t="n"/>
       <c r="I217" s="11" t="n"/>
       <c r="J217" s="9">
@@ -8890,30 +5866,16 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A218" s="11" t="n"/>
       <c r="B218" s="9">
         <f>IF(A218="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A218,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C218" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C218" s="4" t="n"/>
       <c r="D218" s="4" t="n"/>
-      <c r="E218" s="4" t="inlineStr">
-        <is>
-          <t>Winner G7</t>
-        </is>
-      </c>
+      <c r="E218" s="4" t="n"/>
       <c r="F218" s="11" t="n"/>
-      <c r="G218" s="4" t="inlineStr">
-        <is>
-          <t>Winner G8</t>
-        </is>
-      </c>
+      <c r="G218" s="4" t="n"/>
       <c r="H218" s="11" t="n"/>
       <c r="I218" s="11" t="n"/>
       <c r="J218" s="9">
@@ -8927,30 +5889,16 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A219" s="11" t="n"/>
       <c r="B219" s="9">
         <f>IF(A219="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A219,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C219" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C219" s="4" t="n"/>
       <c r="D219" s="4" t="n"/>
-      <c r="E219" s="4" t="inlineStr">
-        <is>
-          <t>Winner G9</t>
-        </is>
-      </c>
+      <c r="E219" s="4" t="n"/>
       <c r="F219" s="11" t="n"/>
-      <c r="G219" s="4" t="inlineStr">
-        <is>
-          <t>Winner G10</t>
-        </is>
-      </c>
+      <c r="G219" s="4" t="n"/>
       <c r="H219" s="11" t="n"/>
       <c r="I219" s="11" t="n"/>
       <c r="J219" s="9">
@@ -8964,30 +5912,16 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A220" s="11" t="n"/>
       <c r="B220" s="9">
         <f>IF(A220="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A220,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C220" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C220" s="4" t="n"/>
       <c r="D220" s="4" t="n"/>
-      <c r="E220" s="4" t="inlineStr">
-        <is>
-          <t>Winner G33</t>
-        </is>
-      </c>
+      <c r="E220" s="4" t="n"/>
       <c r="F220" s="11" t="n"/>
-      <c r="G220" s="4" t="inlineStr">
-        <is>
-          <t>Winner G34</t>
-        </is>
-      </c>
+      <c r="G220" s="4" t="n"/>
       <c r="H220" s="11" t="n"/>
       <c r="I220" s="11" t="n"/>
       <c r="J220" s="9">
@@ -9001,30 +5935,16 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A221" s="11" t="n"/>
       <c r="B221" s="9">
         <f>IF(A221="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A221,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C221" s="4" t="n"/>
       <c r="D221" s="4" t="n"/>
-      <c r="E221" s="4" t="inlineStr">
-        <is>
-          <t>Winner G35</t>
-        </is>
-      </c>
+      <c r="E221" s="4" t="n"/>
       <c r="F221" s="11" t="n"/>
-      <c r="G221" s="4" t="inlineStr">
-        <is>
-          <t>Winner G36</t>
-        </is>
-      </c>
+      <c r="G221" s="4" t="n"/>
       <c r="H221" s="11" t="n"/>
       <c r="I221" s="11" t="n"/>
       <c r="J221" s="9">
@@ -9038,30 +5958,16 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A222" s="11" t="n"/>
       <c r="B222" s="9">
         <f>IF(A222="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A222,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C222" s="4" t="n"/>
       <c r="D222" s="4" t="n"/>
-      <c r="E222" s="4" t="inlineStr">
-        <is>
-          <t>Winner G37</t>
-        </is>
-      </c>
+      <c r="E222" s="4" t="n"/>
       <c r="F222" s="11" t="n"/>
-      <c r="G222" s="4" t="inlineStr">
-        <is>
-          <t>Winner G38</t>
-        </is>
-      </c>
+      <c r="G222" s="4" t="n"/>
       <c r="H222" s="11" t="n"/>
       <c r="I222" s="11" t="n"/>
       <c r="J222" s="9">
@@ -9075,30 +5981,16 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A223" s="11" t="n"/>
       <c r="B223" s="9">
         <f>IF(A223="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A223,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C223" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C223" s="4" t="n"/>
       <c r="D223" s="4" t="n"/>
-      <c r="E223" s="4" t="inlineStr">
-        <is>
-          <t>Winner G39</t>
-        </is>
-      </c>
+      <c r="E223" s="4" t="n"/>
       <c r="F223" s="11" t="n"/>
-      <c r="G223" s="4" t="inlineStr">
-        <is>
-          <t>Winner G40</t>
-        </is>
-      </c>
+      <c r="G223" s="4" t="n"/>
       <c r="H223" s="11" t="n"/>
       <c r="I223" s="11" t="n"/>
       <c r="J223" s="9">
@@ -9112,30 +6004,16 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A224" s="11" t="n"/>
       <c r="B224" s="9">
         <f>IF(A224="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A224,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C224" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C224" s="4" t="n"/>
       <c r="D224" s="4" t="n"/>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>Winner G49</t>
-        </is>
-      </c>
+      <c r="E224" s="4" t="n"/>
       <c r="F224" s="11" t="n"/>
-      <c r="G224" s="4" t="inlineStr">
-        <is>
-          <t>Winner G50</t>
-        </is>
-      </c>
+      <c r="G224" s="4" t="n"/>
       <c r="H224" s="11" t="n"/>
       <c r="I224" s="11" t="n"/>
       <c r="J224" s="9">
@@ -9149,30 +6027,16 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A225" s="11" t="n"/>
       <c r="B225" s="9">
         <f>IF(A225="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A225,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C225" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C225" s="4" t="n"/>
       <c r="D225" s="4" t="n"/>
-      <c r="E225" s="4" t="inlineStr">
-        <is>
-          <t>Winner G51</t>
-        </is>
-      </c>
+      <c r="E225" s="4" t="n"/>
       <c r="F225" s="11" t="n"/>
-      <c r="G225" s="4" t="inlineStr">
-        <is>
-          <t>Winner G52</t>
-        </is>
-      </c>
+      <c r="G225" s="4" t="n"/>
       <c r="H225" s="11" t="n"/>
       <c r="I225" s="11" t="n"/>
       <c r="J225" s="9">
@@ -9186,30 +6050,16 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="A226" s="11" t="n"/>
       <c r="B226" s="9">
         <f>IF(A226="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A226,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C226" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C226" s="4" t="n"/>
       <c r="D226" s="4" t="n"/>
-      <c r="E226" s="4" t="inlineStr">
-        <is>
-          <t>Winner G29</t>
-        </is>
-      </c>
+      <c r="E226" s="4" t="n"/>
       <c r="F226" s="11" t="n"/>
-      <c r="G226" s="4" t="inlineStr">
-        <is>
-          <t>Winner G30</t>
-        </is>
-      </c>
+      <c r="G226" s="4" t="n"/>
       <c r="H226" s="11" t="n"/>
       <c r="I226" s="11" t="n"/>
       <c r="J226" s="9">
@@ -9223,30 +6073,16 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A227" s="11" t="n"/>
       <c r="B227" s="9">
         <f>IF(A227="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A227,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C227" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C227" s="4" t="n"/>
       <c r="D227" s="4" t="n"/>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>Winner G41</t>
-        </is>
-      </c>
+      <c r="E227" s="4" t="n"/>
       <c r="F227" s="11" t="n"/>
-      <c r="G227" s="4" t="inlineStr">
-        <is>
-          <t>Winner G42</t>
-        </is>
-      </c>
+      <c r="G227" s="4" t="n"/>
       <c r="H227" s="11" t="n"/>
       <c r="I227" s="11" t="n"/>
       <c r="J227" s="9">
@@ -9260,30 +6096,16 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A228" s="11" t="n"/>
       <c r="B228" s="9">
         <f>IF(A228="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A228,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C228" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C228" s="4" t="n"/>
       <c r="D228" s="4" t="n"/>
-      <c r="E228" s="4" t="inlineStr">
-        <is>
-          <t>Winner G43</t>
-        </is>
-      </c>
+      <c r="E228" s="4" t="n"/>
       <c r="F228" s="11" t="n"/>
-      <c r="G228" s="4" t="inlineStr">
-        <is>
-          <t>Winner G44</t>
-        </is>
-      </c>
+      <c r="G228" s="4" t="n"/>
       <c r="H228" s="11" t="n"/>
       <c r="I228" s="11" t="n"/>
       <c r="J228" s="9">
@@ -9297,30 +6119,16 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A229" s="11" t="n"/>
       <c r="B229" s="9">
         <f>IF(A229="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A229,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C229" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C229" s="4" t="n"/>
       <c r="D229" s="4" t="n"/>
-      <c r="E229" s="4" t="inlineStr">
-        <is>
-          <t>Winner G45</t>
-        </is>
-      </c>
+      <c r="E229" s="4" t="n"/>
       <c r="F229" s="11" t="n"/>
-      <c r="G229" s="4" t="inlineStr">
-        <is>
-          <t>Winner G46</t>
-        </is>
-      </c>
+      <c r="G229" s="4" t="n"/>
       <c r="H229" s="11" t="n"/>
       <c r="I229" s="11" t="n"/>
       <c r="J229" s="9">
@@ -9334,30 +6142,16 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="A230" s="11" t="n"/>
       <c r="B230" s="9">
         <f>IF(A230="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A230,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C230" s="4" t="n"/>
       <c r="D230" s="4" t="n"/>
-      <c r="E230" s="4" t="inlineStr">
-        <is>
-          <t>Winner G47</t>
-        </is>
-      </c>
+      <c r="E230" s="4" t="n"/>
       <c r="F230" s="11" t="n"/>
-      <c r="G230" s="4" t="inlineStr">
-        <is>
-          <t>Winner G48</t>
-        </is>
-      </c>
+      <c r="G230" s="4" t="n"/>
       <c r="H230" s="11" t="n"/>
       <c r="I230" s="11" t="n"/>
       <c r="J230" s="9">
@@ -9371,30 +6165,16 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A231" s="11" t="n"/>
       <c r="B231" s="9">
         <f>IF(A231="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A231,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C231" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C231" s="4" t="n"/>
       <c r="D231" s="4" t="n"/>
-      <c r="E231" s="4" t="inlineStr">
-        <is>
-          <t>Winner G53</t>
-        </is>
-      </c>
+      <c r="E231" s="4" t="n"/>
       <c r="F231" s="11" t="n"/>
-      <c r="G231" s="4" t="inlineStr">
-        <is>
-          <t>Winner G54</t>
-        </is>
-      </c>
+      <c r="G231" s="4" t="n"/>
       <c r="H231" s="11" t="n"/>
       <c r="I231" s="11" t="n"/>
       <c r="J231" s="9">
@@ -9408,30 +6188,16 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="A232" s="11" t="n"/>
       <c r="B232" s="9">
         <f>IF(A232="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A232,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C232" s="4" t="n"/>
       <c r="D232" s="4" t="n"/>
-      <c r="E232" s="4" t="inlineStr">
-        <is>
-          <t>Winner G55</t>
-        </is>
-      </c>
+      <c r="E232" s="4" t="n"/>
       <c r="F232" s="11" t="n"/>
-      <c r="G232" s="4" t="inlineStr">
-        <is>
-          <t>Winner G56</t>
-        </is>
-      </c>
+      <c r="G232" s="4" t="n"/>
       <c r="H232" s="11" t="n"/>
       <c r="I232" s="11" t="n"/>
       <c r="J232" s="9">
@@ -9445,30 +6211,16 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A233" s="11" t="n"/>
       <c r="B233" s="9">
         <f>IF(A233="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A233,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C233" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C233" s="4" t="n"/>
       <c r="D233" s="4" t="n"/>
-      <c r="E233" s="4" t="inlineStr">
-        <is>
-          <t>Winner G57</t>
-        </is>
-      </c>
+      <c r="E233" s="4" t="n"/>
       <c r="F233" s="11" t="n"/>
-      <c r="G233" s="4" t="inlineStr">
-        <is>
-          <t>Winner G58</t>
-        </is>
-      </c>
+      <c r="G233" s="4" t="n"/>
       <c r="H233" s="11" t="n"/>
       <c r="I233" s="11" t="n"/>
       <c r="J233" s="9">
@@ -9482,30 +6234,16 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="A234" s="11" t="n"/>
       <c r="B234" s="9">
         <f>IF(A234="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A234,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C234" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C234" s="4" t="n"/>
       <c r="D234" s="4" t="n"/>
-      <c r="E234" s="4" t="inlineStr">
-        <is>
-          <t>Winner G59</t>
-        </is>
-      </c>
+      <c r="E234" s="4" t="n"/>
       <c r="F234" s="11" t="n"/>
-      <c r="G234" s="4" t="inlineStr">
-        <is>
-          <t>Winner G60</t>
-        </is>
-      </c>
+      <c r="G234" s="4" t="n"/>
       <c r="H234" s="11" t="n"/>
       <c r="I234" s="11" t="n"/>
       <c r="J234" s="9">
@@ -9519,30 +6257,16 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="A235" s="11" t="n"/>
       <c r="B235" s="9">
         <f>IF(A235="","",IFERROR(INDEX(Lists!$G$2:$G$7,MATCH(A235,Lists!$F$2:$F$7,0)),"?"))</f>
         <v/>
       </c>
-      <c r="C235" s="4" t="inlineStr">
-        <is>
-          <t>6A D2</t>
-        </is>
-      </c>
+      <c r="C235" s="4" t="n"/>
       <c r="D235" s="4" t="n"/>
-      <c r="E235" s="4" t="inlineStr">
-        <is>
-          <t>Winner G61</t>
-        </is>
-      </c>
+      <c r="E235" s="4" t="n"/>
       <c r="F235" s="11" t="n"/>
-      <c r="G235" s="4" t="inlineStr">
-        <is>
-          <t>Winner G62</t>
-        </is>
-      </c>
+      <c r="G235" s="4" t="n"/>
       <c r="H235" s="11" t="n"/>
       <c r="I235" s="11" t="n"/>
       <c r="J235" s="9">
